--- a/Library/Private/LCSC_Classified/exports/LCSC_Classified_all_parts_by_category.xlsx
+++ b/Library/Private/LCSC_Classified/exports/LCSC_Classified_all_parts_by_category.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rf31c367993784444"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capacitors" sheetId="2" r:id="R2e71fb0b85154f11"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Circuit Protection" sheetId="3" r:id="Ref9fa5a597ca43e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Connectors" sheetId="4" r:id="Recbdd310ac0646e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crystals &amp; Oscillators" sheetId="5" r:id="R2d6c9fb92ea944c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diodes" sheetId="6" r:id="Rb643a33d2ad24b64"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Embedded Processors &amp; Controlle" sheetId="7" r:id="R1841400fec454de7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="8" r:id="Rfba5c20ca24c44a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inductors &amp; Coils" sheetId="9" r:id="R45466db8157545e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Industrial Controls" sheetId="10" r:id="Rfbf2cb55a2de4182"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="11" r:id="R41e050312dd841b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Magnetic Sensors" sheetId="12" r:id="R7c8aab3fa9f645c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Memory" sheetId="13" r:id="R9368854945834659"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Motor Driver ICs" sheetId="14" r:id="R8ae183ebfee3479f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Optoelectronics" sheetId="15" r:id="R608dc30956fc439f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Power Management" sheetId="16" r:id="R7cd948627b004d86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resistors" sheetId="17" r:id="Rf7d54db565244b43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensors" sheetId="18" r:id="R97efe04551754849"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Switches" sheetId="19" r:id="Rbc6b136dc2394d75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transistors" sheetId="20" r:id="R8d839dd1a87c4589"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R7a976f31ba7444cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capacitors" sheetId="2" r:id="R47aa9969decc43f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Circuit Protection" sheetId="3" r:id="Rcca31500105243c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Connectors" sheetId="4" r:id="R95214b3f90a74224"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crystals &amp; Oscillators" sheetId="5" r:id="R943e323ad79f467d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diodes" sheetId="6" r:id="R6868bfca1bb54164"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Embedded Processors &amp; Controlle" sheetId="7" r:id="R68aefa0aea44437c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="8" r:id="R1baf3784d6624f0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inductors &amp; Coils" sheetId="9" r:id="Raccd3f0e782c4068"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Industrial Controls" sheetId="10" r:id="R04ba967ddfd949be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="11" r:id="R4c5ce0263dbf4d0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Magnetic Sensors" sheetId="12" r:id="R2bfffa7dd5da47d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Memory" sheetId="13" r:id="R073dcc2ebc4b44b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Motor Driver ICs" sheetId="14" r:id="R2ce590f6559d47bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Optoelectronics" sheetId="15" r:id="R84dd578e102e416a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Power Management" sheetId="16" r:id="Ra99cd449f6684449"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resistors" sheetId="17" r:id="R0e5c22c3dc1846c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensors" sheetId="18" r:id="Re7246011e4324b36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Switches" sheetId="19" r:id="R9e8bcd8dadf849d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transistors" sheetId="20" r:id="R6f5babc7eecc4bae"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -383,8 +383,8 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Table_LCSCMagneticSensors" displayName="Table_LCSCMagneticSensors" ref="A4:V7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:V7"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Table_LCSCMagneticSensors" displayName="Table_LCSCMagneticSensors" ref="A4:V8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:V8"/>
   <x:tableColumns count="22">
     <x:tableColumn id="1" name="LCSC"/>
     <x:tableColumn id="2" name="MPN"/>
@@ -538,8 +538,8 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="Table_LCSCResistors" displayName="Table_LCSCResistors" ref="A4:V31" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:V31"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="Table_LCSCResistors" displayName="Table_LCSCResistors" ref="A4:V34" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:V34"/>
   <x:tableColumns count="22">
     <x:tableColumn id="1" name="LCSC"/>
     <x:tableColumn id="2" name="MPN"/>
@@ -631,8 +631,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table_LCSCCapacitors" displayName="Table_LCSCCapacitors" ref="A4:V31" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:V31"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table_LCSCCapacitors" displayName="Table_LCSCCapacitors" ref="A4:V35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:V35"/>
   <x:tableColumns count="22">
     <x:tableColumn id="1" name="LCSC"/>
     <x:tableColumn id="2" name="MPN"/>
@@ -693,8 +693,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table_LCSCCircuitProtection" displayName="Table_LCSCCircuitProtection" ref="A4:V5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:V5"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table_LCSCCircuitProtection" displayName="Table_LCSCCircuitProtection" ref="A4:V6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:V6"/>
   <x:tableColumns count="22">
     <x:tableColumn id="1" name="LCSC"/>
     <x:tableColumn id="2" name="MPN"/>
@@ -724,8 +724,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table_LCSCConnectors" displayName="Table_LCSCConnectors" ref="A4:V11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:V11"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table_LCSCConnectors" displayName="Table_LCSCConnectors" ref="A4:V12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:V12"/>
   <x:tableColumns count="22">
     <x:tableColumn id="1" name="LCSC"/>
     <x:tableColumn id="2" name="MPN"/>
@@ -1158,19 +1158,19 @@
         <x:v>Capacitors</x:v>
       </x:c>
       <x:c r="C5" s="5" t="n">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D5" s="5" t="n">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E5" s="5" t="n">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F5" s="5" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G5" s="5" t="n">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H5" s="5" t="n">
         <x:v>0</x:v>
@@ -1184,19 +1184,19 @@
         <x:v>Circuit Protection</x:v>
       </x:c>
       <x:c r="C6" s="5" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D6" s="5" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E6" s="5" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F6" s="5" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G6" s="5" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H6" s="5" t="n">
         <x:v>0</x:v>
@@ -1210,19 +1210,19 @@
         <x:v>Connectors</x:v>
       </x:c>
       <x:c r="C7" s="5" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D7" s="5" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E7" s="5" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F7" s="5" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G7" s="5" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H7" s="5" t="n">
         <x:v>0</x:v>
@@ -1418,19 +1418,19 @@
         <x:v>Magnetic Sensors</x:v>
       </x:c>
       <x:c r="C15" s="5" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D15" s="5" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E15" s="5" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F15" s="5" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G15" s="5" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H15" s="5" t="n">
         <x:v>0</x:v>
@@ -1548,19 +1548,19 @@
         <x:v>Resistors</x:v>
       </x:c>
       <x:c r="C20" s="5" t="n">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D20" s="5" t="n">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E20" s="5" t="n">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F20" s="5" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G20" s="5" t="n">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H20" s="5" t="n">
         <x:v>0</x:v>
@@ -1647,7 +1647,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91f9bfac3b024e6c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc593b0ecf7ae4974"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1826,7 +1826,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6bd0d40772f84c5c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re972e3cb294245bf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2127,7 +2127,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd95bb8374854630"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9816a7dfede4ced"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2167,7 +2167,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="2" t="str">
-        <x:v>类别：Magnetic Sensors；记录数：3；来源：all_parts.csv</x:v>
+        <x:v>类别：Magnetic Sensors；记录数：4；来源：all_parts.csv</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -2240,43 +2240,39 @@
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
       <x:c r="A5" s="7" t="str">
-        <x:v>C49257133</x:v>
+        <x:v>C2913974</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>MT6701QT-ACD</x:v>
+        <x:v>MT6701QT-STD</x:v>
       </x:c>
       <x:c r="C5" s="7" t="str">
-        <x:v>NOVOSENSE</x:v>
+        <x:v>NOVOSENSE(纳芯微)</x:v>
       </x:c>
       <x:c r="D5" s="7" t="str">
-        <x:v>QFN-16(3x3) Angle, Linear Position Measuring</x:v>
+        <x:v>MT6701 QFN-16 magnetic angle sensor, standard variant</x:v>
       </x:c>
       <x:c r="E5" s="7" t="str">
         <x:v>Magnetic Sensors/Angle, Linear Position Measuring</x:v>
       </x:c>
       <x:c r="F5" s="7" t="str">
-        <x:v>MT6701QT-ACD</x:v>
+        <x:v>MT6701QT-STD_C2913974</x:v>
       </x:c>
       <x:c r="G5" s="7" t="str">
         <x:v>VQFN-16_L3.0-W3.0-P0.50-TL-EP1.7</x:v>
       </x:c>
       <x:c r="H5" s="7" t="str">
-        <x:v>暂无料号25</x:v>
+        <x:v>MT6701QT-STD</x:v>
       </x:c>
       <x:c r="I5" s="7" t="str">
-        <x:v>QFN-16(3x3)</x:v>
+        <x:v>QFN-16-EP(3x3)</x:v>
       </x:c>
       <x:c r="J5" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/935357a86952b28e12ac9bd3d186d5d1.pdf?productCode=C49257133</x:v>
-      </x:c>
-      <x:c r="K5" s="7" t="str">
-        <x:v>Rev1.5</x:v>
-      </x:c>
-      <x:c r="L5" s="7" t="str">
-        <x:v>2021-03</x:v>
-      </x:c>
+        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20260616/FEB700C1922508565884FF0A90656B50.pdf</x:v>
+      </x:c>
+      <x:c r="K5" s="7" t="str"/>
+      <x:c r="L5" s="7" t="str"/>
       <x:c r="M5" s="7" t="str">
-        <x:v>../datasheets/C49257133/MT6701_Rev1.5_2021.03.pdf</x:v>
+        <x:v>../datasheets/C2913974/MT6701QT-STD.pdf</x:v>
       </x:c>
       <x:c r="N5" s="7" t="str"/>
       <x:c r="O5" s="7" t="str">
@@ -2286,59 +2282,63 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q5" s="7" t="str">
-        <x:v>QFN-16/3~5V</x:v>
+        <x:v>QFN-16-EP(3x3)</x:v>
       </x:c>
       <x:c r="R5" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C49257133.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C2913974.html</x:v>
       </x:c>
       <x:c r="S5" s="7" t="str">
-        <x:v>Package: QFN-16(3x3); Operating Temperature: -40℃~+125℃; Number of Conjugate Points of UVW: 16; Supply Current: 10mA; Features: Incremental encoder output;Programmable hysteresis;Magnetic field too high/low warning; Voltage - Supply: 3.3V~5V; Out Type: SSI;ABZ;PWM; Number of ABZ Pulses: 1024; Rotate Speed: 55000rpm; Minimum Field: 20mT</x:v>
+        <x:v>Package: QFN-16(3x3); Supply: 3V~5.5V; Interface: SSI/ABZ/PWM</x:v>
       </x:c>
       <x:c r="T5" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y189.xls; Designators: BOM_PASTER_8984112A_Y189.xls: U1</x:v>
+        <x:v>EBOM BOM_QS01_GD32F503_V1.10; designator U5.</x:v>
       </x:c>
       <x:c r="U5" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V5" s="7" t="str">
-        <x:v>legacy_import</x:v>
+        <x:v>EBOM_V1.10</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="24" customHeight="1">
       <x:c r="A6" s="7" t="str">
-        <x:v>C7433196</x:v>
+        <x:v>C49257133</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
-        <x:v>MA735GGU-Z</x:v>
+        <x:v>MT6701QT-ACD</x:v>
       </x:c>
       <x:c r="C6" s="7" t="str">
-        <x:v>MPS(芯源)</x:v>
+        <x:v>NOVOSENSE</x:v>
       </x:c>
       <x:c r="D6" s="7" t="str">
-        <x:v>MA735 magnetic angle sensor, QFN-14 2x2mm</x:v>
+        <x:v>QFN-16(3x3) Angle, Linear Position Measuring</x:v>
       </x:c>
       <x:c r="E6" s="7" t="str">
         <x:v>Magnetic Sensors/Angle, Linear Position Measuring</x:v>
       </x:c>
       <x:c r="F6" s="7" t="str">
-        <x:v>MA735GGU-Z</x:v>
+        <x:v>MT6701QT-ACD</x:v>
       </x:c>
       <x:c r="G6" s="7" t="str">
-        <x:v>UTQFN-14_L2.0-W2.0-P0.40-TL</x:v>
+        <x:v>VQFN-16_L3.0-W3.0-P0.50-TL-EP1.7</x:v>
       </x:c>
       <x:c r="H6" s="7" t="str">
-        <x:v>MA735GGU-Z</x:v>
+        <x:v>暂无料号25</x:v>
       </x:c>
       <x:c r="I6" s="7" t="str">
-        <x:v>UTQFN-14(2x2)</x:v>
+        <x:v>QFN-16(3x3)</x:v>
       </x:c>
       <x:c r="J6" s="7" t="str">
-        <x:v>https://www.lcsc.com/datasheet/C7433196.pdf</x:v>
-      </x:c>
-      <x:c r="K6" s="7" t="str"/>
-      <x:c r="L6" s="7" t="str"/>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/935357a86952b28e12ac9bd3d186d5d1.pdf?productCode=C49257133</x:v>
+      </x:c>
+      <x:c r="K6" s="7" t="str">
+        <x:v>Rev1.5</x:v>
+      </x:c>
+      <x:c r="L6" s="7" t="str">
+        <x:v>2021-03</x:v>
+      </x:c>
       <x:c r="M6" s="7" t="str">
-        <x:v>../datasheets/C7433196/MA735GGU-Z.pdf</x:v>
+        <x:v>../datasheets/C49257133/MT6701_Rev1.5_2021.03.pdf</x:v>
       </x:c>
       <x:c r="N6" s="7" t="str"/>
       <x:c r="O6" s="7" t="str">
@@ -2348,14 +2348,16 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q6" s="7" t="str">
-        <x:v>磁性角度传感器</x:v>
+        <x:v>QFN-16/3~5V</x:v>
       </x:c>
       <x:c r="R6" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C7433196.html</x:v>
-      </x:c>
-      <x:c r="S6" s="7" t="str"/>
+        <x:v>https://www.lcsc.com/product-detail/C49257133.html</x:v>
+      </x:c>
+      <x:c r="S6" s="7" t="str">
+        <x:v>Package: QFN-16(3x3); Operating Temperature: -40℃~+125℃; Number of Conjugate Points of UVW: 16; Supply Current: 10mA; Features: Incremental encoder output;Programmable hysteresis;Magnetic field too high/low warning; Voltage - Supply: 3.3V~5V; Out Type: SSI;ABZ;PWM; Number of ABZ Pulses: 1024; Rotate Speed: 55000rpm; Minimum Field: 20mT</x:v>
+      </x:c>
       <x:c r="T6" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y185.xls: U5; Inferred from magnetic angle sensor description; confirm exact device later; Identity and metadata recovered from the existing verified KiCad symbol.</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y189.xls; Designators: BOM_PASTER_8984112A_Y189.xls: U1</x:v>
       </x:c>
       <x:c r="U6" s="7" t="str">
         <x:v>METADATA_READY</x:v>
@@ -2366,35 +2368,39 @@
     </x:row>
     <x:row r="7" ht="24" customHeight="1">
       <x:c r="A7" s="7" t="str">
-        <x:v>C9900009343</x:v>
+        <x:v>C7433196</x:v>
       </x:c>
       <x:c r="B7" s="7" t="str">
-        <x:v>iC-PVL</x:v>
+        <x:v>MA735GGU-Z</x:v>
       </x:c>
       <x:c r="C7" s="7" t="str">
-        <x:v>IC-HAUS</x:v>
+        <x:v>MPS(芯源)</x:v>
       </x:c>
       <x:c r="D7" s="7" t="str">
-        <x:v>iC-PVL QFN16 4x4 Linear Hall Sensor</x:v>
+        <x:v>MA735 magnetic angle sensor, QFN-14 2x2mm</x:v>
       </x:c>
       <x:c r="E7" s="7" t="str">
         <x:v>Magnetic Sensors/Angle, Linear Position Measuring</x:v>
       </x:c>
-      <x:c r="F7" s="7" t="str"/>
-      <x:c r="G7" s="7" t="str"/>
+      <x:c r="F7" s="7" t="str">
+        <x:v>MA735GGU-Z</x:v>
+      </x:c>
+      <x:c r="G7" s="7" t="str">
+        <x:v>UTQFN-14_L2.0-W2.0-P0.40-TL</x:v>
+      </x:c>
       <x:c r="H7" s="7" t="str">
-        <x:v>iC-PVL</x:v>
+        <x:v>MA735GGU-Z</x:v>
       </x:c>
       <x:c r="I7" s="7" t="str">
-        <x:v>QFN16(4x4)</x:v>
+        <x:v>UTQFN-14(2x2)</x:v>
       </x:c>
       <x:c r="J7" s="7" t="str">
-        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20260917/41A48149B31B33F1461152DD9086207D.pdf</x:v>
+        <x:v>https://www.lcsc.com/datasheet/C7433196.pdf</x:v>
       </x:c>
       <x:c r="K7" s="7" t="str"/>
       <x:c r="L7" s="7" t="str"/>
       <x:c r="M7" s="7" t="str">
-        <x:v>../datasheets/C9900009343/iC-PVL.pdf</x:v>
+        <x:v>../datasheets/C7433196/MA735GGU-Z.pdf</x:v>
       </x:c>
       <x:c r="N7" s="7" t="str"/>
       <x:c r="O7" s="7" t="str">
@@ -2404,31 +2410,87 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q7" s="7" t="str">
+        <x:v>磁性角度传感器</x:v>
+      </x:c>
+      <x:c r="R7" s="7" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C7433196.html</x:v>
+      </x:c>
+      <x:c r="S7" s="7" t="str"/>
+      <x:c r="T7" s="7" t="str">
+        <x:v>Sources: BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y185.xls: U5; Inferred from magnetic angle sensor description; confirm exact device later; Identity and metadata recovered from the existing verified KiCad symbol.</x:v>
+      </x:c>
+      <x:c r="U7" s="7" t="str">
+        <x:v>METADATA_READY</x:v>
+      </x:c>
+      <x:c r="V7" s="7" t="str">
+        <x:v>legacy_import</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="24" customHeight="1">
+      <x:c r="A8" s="7" t="str">
+        <x:v>C9900009343</x:v>
+      </x:c>
+      <x:c r="B8" s="7" t="str">
+        <x:v>iC-PVL</x:v>
+      </x:c>
+      <x:c r="C8" s="7" t="str">
+        <x:v>IC-HAUS</x:v>
+      </x:c>
+      <x:c r="D8" s="7" t="str">
+        <x:v>iC-PVL QFN16 4x4 Linear Hall Sensor</x:v>
+      </x:c>
+      <x:c r="E8" s="7" t="str">
+        <x:v>Magnetic Sensors/Angle, Linear Position Measuring</x:v>
+      </x:c>
+      <x:c r="F8" s="7" t="str"/>
+      <x:c r="G8" s="7" t="str"/>
+      <x:c r="H8" s="7" t="str">
+        <x:v>iC-PVL</x:v>
+      </x:c>
+      <x:c r="I8" s="7" t="str">
         <x:v>QFN16(4x4)</x:v>
       </x:c>
-      <x:c r="R7" s="7" t="str">
+      <x:c r="J8" s="7" t="str">
+        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20260917/41A48149B31B33F1461152DD9086207D.pdf</x:v>
+      </x:c>
+      <x:c r="K8" s="7" t="str"/>
+      <x:c r="L8" s="7" t="str"/>
+      <x:c r="M8" s="7" t="str">
+        <x:v>../datasheets/C9900009343/iC-PVL.pdf</x:v>
+      </x:c>
+      <x:c r="N8" s="7" t="str"/>
+      <x:c r="O8" s="7" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="P8" s="7" t="str">
+        <x:v>LCSC</x:v>
+      </x:c>
+      <x:c r="Q8" s="7" t="str">
+        <x:v>QFN16(4x4)</x:v>
+      </x:c>
+      <x:c r="R8" s="7" t="str">
         <x:v>https://item.szlcsc.com/217651.html</x:v>
       </x:c>
-      <x:c r="S7" s="7" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Package: QFN16-4x4; Function: linear Hall sensor; Current replacement reference: C46526385</x:v>
       </x:c>
-      <x:c r="T7" s="7" t="str">
+      <x:c r="T8" s="7" t="str">
         <x:v>Designators: Y193-U2; Y43-U3; Z300BL-U3</x:v>
       </x:c>
-      <x:c r="U7" s="7" t="str">
-        <x:v>METADATA_READY</x:v>
-      </x:c>
-      <x:c r="V7" s="7" t="str">
+      <x:c r="U8" s="7" t="str">
+        <x:v>METADATA_READY</x:v>
+      </x:c>
+      <x:c r="V8" s="7" t="str">
         <x:v>Y193; Y43; Z300BL</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="U5:U7">
+  <x:conditionalFormatting sqref="U5:U8">
     <x:cfRule type="containsText" dxfId="10" priority="1" operator="containsText" text="CLASSIFIED_PARTIAL"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31ec91bf57964d9e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80a4f073fef64788"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2607,7 +2669,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47f5ea0fbdf64ea3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref46fb44bc7849e0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2912,7 +2974,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Racd7865a6e544e19"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red8602f1e4eb4179"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3215,7 +3277,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc77f332d9bfc4726"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2c3a2d06b324d42"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3694,7 +3756,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c2ddf0ddb004e31"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e76da66e3c642f2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3734,7 +3796,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="2" t="str">
-        <x:v>类别：Resistors；记录数：27；来源：all_parts.csv</x:v>
+        <x:v>类别：Resistors；记录数：30；来源：all_parts.csv</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -3993,39 +4055,39 @@
     </x:row>
     <x:row r="8" ht="24" customHeight="1">
       <x:c r="A8" s="7" t="str">
-        <x:v>C106225</x:v>
+        <x:v>C106224</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
-        <x:v>RC0201FR-0710KL</x:v>
+        <x:v>RC0201FR-07100KL</x:v>
       </x:c>
       <x:c r="C8" s="7" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>YAGEO(国巨)</x:v>
       </x:c>
       <x:c r="D8" s="7" t="str">
-        <x:v>50mW 10kΩ 25V Thick Film Resistor ±1% ±200ppm/℃ 0201 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>100k 1% 0201 chip resistor</x:v>
       </x:c>
       <x:c r="E8" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F8" s="7" t="str">
-        <x:v>R_10kohm_0201</x:v>
+        <x:v>R_100k_0201</x:v>
       </x:c>
       <x:c r="G8" s="7" t="str">
-        <x:v>ExternalDriver_RC0201FR-0710KL</x:v>
+        <x:v>R_0201_0603Metric</x:v>
       </x:c>
       <x:c r="H8" s="7" t="str">
-        <x:v>10kΩ</x:v>
+        <x:v>100k</x:v>
       </x:c>
       <x:c r="I8" s="7" t="str">
         <x:v>0201</x:v>
       </x:c>
       <x:c r="J8" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C106225</x:v>
+        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20250610/89E4D743C004A82A45145C7A2CC3A578.pdf</x:v>
       </x:c>
       <x:c r="K8" s="7" t="str"/>
       <x:c r="L8" s="7" t="str"/>
       <x:c r="M8" s="7" t="str">
-        <x:v>../datasheets/C106225/RC0201FR-0710KL.pdf</x:v>
+        <x:v>../datasheets/C106224/RC0201FR-07100KL.pdf</x:v>
       </x:c>
       <x:c r="N8" s="7" t="str"/>
       <x:c r="O8" s="7" t="str">
@@ -4035,78 +4097,78 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str">
-        <x:v>RC0201FR-0710KL</x:v>
+        <x:v>R0201</x:v>
       </x:c>
       <x:c r="R8" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C106225.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C106224.html</x:v>
       </x:c>
       <x:c r="S8" s="7" t="str">
-        <x:v>Package: 0201; Power(Watts): 50mW; Resistance: 10kΩ; Voltage Rating: 25V; Operating Temperature: -55℃~+125℃; Type: Thick Film Resistor; Tolerance: ±1%; Temperature Coefficient: ±200ppm/℃</x:v>
+        <x:v>Package: 0201; Resistance: 100k; Tolerance: 1%</x:v>
       </x:c>
       <x:c r="T8" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R2,R32,R33,R39,R49,R50,R51; BOM_PASTER_8984112A_Y185.xls: R2,R3,R4,R7,R9,R11</x:v>
+        <x:v>EBOM BOM_QS01_GD32F503_V1.10; designator R17.</x:v>
       </x:c>
       <x:c r="U8" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V8" s="7" t="str">
-        <x:v>legacy_import</x:v>
+        <x:v>EBOM_V1.10</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="24" customHeight="1">
       <x:c r="A9" s="7" t="str">
-        <x:v>C106226</x:v>
+        <x:v>C106225</x:v>
       </x:c>
       <x:c r="B9" s="7" t="str">
-        <x:v>RC0201FR-0710RL</x:v>
+        <x:v>RC0201FR-0710KL</x:v>
       </x:c>
       <x:c r="C9" s="7" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D9" s="7" t="str">
-        <x:v>50mW 10Ω 25V Thick Film Resistor ±1% -100ppm/℃~+350ppm/℃ 0201 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>50mW 10kΩ 25V Thick Film Resistor ±1% ±200ppm/℃ 0201 Chip Resistor - Surface Mount RoHS</x:v>
       </x:c>
       <x:c r="E9" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F9" s="7" t="str">
-        <x:v>R_10ohm_0201</x:v>
+        <x:v>R_10kohm_0201</x:v>
       </x:c>
       <x:c r="G9" s="7" t="str">
-        <x:v>ExternalDriver_RC0201FR-0710RL</x:v>
+        <x:v>ExternalDriver_RC0201FR-0710KL</x:v>
       </x:c>
       <x:c r="H9" s="7" t="str">
-        <x:v>10Ω</x:v>
+        <x:v>10kΩ</x:v>
       </x:c>
       <x:c r="I9" s="7" t="str">
         <x:v>0201</x:v>
       </x:c>
       <x:c r="J9" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C106226</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C106225</x:v>
       </x:c>
       <x:c r="K9" s="7" t="str"/>
       <x:c r="L9" s="7" t="str"/>
       <x:c r="M9" s="7" t="str">
-        <x:v>../datasheets/C106226/RC0201FR-0710RL.pdf</x:v>
+        <x:v>../datasheets/C106225/RC0201FR-0710KL.pdf</x:v>
       </x:c>
       <x:c r="N9" s="7" t="str"/>
       <x:c r="O9" s="7" t="str">
-        <x:v>OutOfStock</x:v>
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="P9" s="7" t="str">
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q9" s="7" t="str">
-        <x:v>RC0201FR-0710RL</x:v>
+        <x:v>RC0201FR-0710KL</x:v>
       </x:c>
       <x:c r="R9" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C106226.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C106225.html</x:v>
       </x:c>
       <x:c r="S9" s="7" t="str">
-        <x:v>Package: 0201; Power(Watts): 50mW; Resistance: 10Ω; Voltage Rating: 25V; Operating Temperature: -55℃~+125℃; Type: Thick Film Resistor; Tolerance: ±1%; Temperature Coefficient: -100ppm/℃~+350ppm/℃</x:v>
+        <x:v>Package: 0201; Power(Watts): 50mW; Resistance: 10kΩ; Voltage Rating: 25V; Operating Temperature: -55℃~+125℃; Type: Thick Film Resistor; Tolerance: ±1%; Temperature Coefficient: ±200ppm/℃</x:v>
       </x:c>
       <x:c r="T9" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R21,R22; BOM_PASTER_8984112A_Y185.xls: R1,R10</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R2,R32,R33,R39,R49,R50,R51; BOM_PASTER_8984112A_Y185.xls: R2,R3,R4,R7,R9,R11</x:v>
       </x:c>
       <x:c r="U9" s="7" t="str">
         <x:v>METADATA_READY</x:v>
@@ -4117,58 +4179,58 @@
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
       <x:c r="A10" s="7" t="str">
-        <x:v>C106227</x:v>
+        <x:v>C106226</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>RC0201FR-070RL</x:v>
+        <x:v>RC0201FR-0710RL</x:v>
       </x:c>
       <x:c r="C10" s="7" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D10" s="7" t="str">
-        <x:v>50mW 0Ω 25V Thick Film Resistor ±1% 0201 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>50mW 10Ω 25V Thick Film Resistor ±1% -100ppm/℃~+350ppm/℃ 0201 Chip Resistor - Surface Mount RoHS</x:v>
       </x:c>
       <x:c r="E10" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F10" s="7" t="str">
-        <x:v>R_0ohm_0201</x:v>
+        <x:v>R_10ohm_0201</x:v>
       </x:c>
       <x:c r="G10" s="7" t="str">
-        <x:v>ExternalDriver_RC0201FR-070RL</x:v>
+        <x:v>ExternalDriver_RC0201FR-0710RL</x:v>
       </x:c>
       <x:c r="H10" s="7" t="str">
-        <x:v>0Ω</x:v>
+        <x:v>10Ω</x:v>
       </x:c>
       <x:c r="I10" s="7" t="str">
         <x:v>0201</x:v>
       </x:c>
       <x:c r="J10" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C106227</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C106226</x:v>
       </x:c>
       <x:c r="K10" s="7" t="str"/>
       <x:c r="L10" s="7" t="str"/>
       <x:c r="M10" s="7" t="str">
-        <x:v>../datasheets/C106227/RC0201FR-070RL.pdf</x:v>
+        <x:v>../datasheets/C106226/RC0201FR-0710RL.pdf</x:v>
       </x:c>
       <x:c r="N10" s="7" t="str"/>
       <x:c r="O10" s="7" t="str">
-        <x:v>Active</x:v>
+        <x:v>OutOfStock</x:v>
       </x:c>
       <x:c r="P10" s="7" t="str">
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str">
-        <x:v>RC0201FR-070RL</x:v>
+        <x:v>RC0201FR-0710RL</x:v>
       </x:c>
       <x:c r="R10" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C106227.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C106226.html</x:v>
       </x:c>
       <x:c r="S10" s="7" t="str">
-        <x:v>Package: 0201; Power(Watts): 50mW; Resistance: 0Ω; Voltage Rating: 25V; Operating Temperature: -55℃~+125℃; Type: Thick Film Resistor; Tolerance: ±1%; Temperature Coefficient: -</x:v>
+        <x:v>Package: 0201; Power(Watts): 50mW; Resistance: 10Ω; Voltage Rating: 25V; Operating Temperature: -55℃~+125℃; Type: Thick Film Resistor; Tolerance: ±1%; Temperature Coefficient: -100ppm/℃~+350ppm/℃</x:v>
       </x:c>
       <x:c r="T10" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R8; BOM_PASTER_8984112A_Y185.xls: R12</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R21,R22; BOM_PASTER_8984112A_Y185.xls: R1,R10</x:v>
       </x:c>
       <x:c r="U10" s="7" t="str">
         <x:v>METADATA_READY</x:v>
@@ -4179,39 +4241,39 @@
     </x:row>
     <x:row r="11" ht="24" customHeight="1">
       <x:c r="A11" s="7" t="str">
-        <x:v>C106231</x:v>
+        <x:v>C106227</x:v>
       </x:c>
       <x:c r="B11" s="7" t="str">
-        <x:v>RC0402FR-070RL</x:v>
+        <x:v>RC0201FR-070RL</x:v>
       </x:c>
       <x:c r="C11" s="7" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D11" s="7" t="str">
-        <x:v>0Ω 62.5mW 50V Thick Film Resistor ±1% 0402 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>50mW 0Ω 25V Thick Film Resistor ±1% 0201 Chip Resistor - Surface Mount RoHS</x:v>
       </x:c>
       <x:c r="E11" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F11" s="7" t="str">
-        <x:v>R_0ohm_0402</x:v>
+        <x:v>R_0ohm_0201</x:v>
       </x:c>
       <x:c r="G11" s="7" t="str">
-        <x:v>R_0402_1005Metric</x:v>
+        <x:v>ExternalDriver_RC0201FR-070RL</x:v>
       </x:c>
       <x:c r="H11" s="7" t="str">
         <x:v>0Ω</x:v>
       </x:c>
       <x:c r="I11" s="7" t="str">
-        <x:v>0402</x:v>
+        <x:v>0201</x:v>
       </x:c>
       <x:c r="J11" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C106231</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C106227</x:v>
       </x:c>
       <x:c r="K11" s="7" t="str"/>
       <x:c r="L11" s="7" t="str"/>
       <x:c r="M11" s="7" t="str">
-        <x:v>../datasheets/C106231/RC0402FR-070RL.pdf</x:v>
+        <x:v>../datasheets/C106227/RC0201FR-070RL.pdf</x:v>
       </x:c>
       <x:c r="N11" s="7" t="str"/>
       <x:c r="O11" s="7" t="str">
@@ -4221,59 +4283,59 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q11" s="7" t="str">
-        <x:v>贴片电阻</x:v>
+        <x:v>RC0201FR-070RL</x:v>
       </x:c>
       <x:c r="R11" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C106231.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C106227.html</x:v>
       </x:c>
       <x:c r="S11" s="7" t="str">
-        <x:v>Package: 0402; Resistance: 0Ω; Power(Watts): 62.5mW; Voltage Rating: 50V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: -; Tolerance: ±1%</x:v>
+        <x:v>Package: 0201; Power(Watts): 50mW; Resistance: 0Ω; Voltage Rating: 25V; Operating Temperature: -55℃~+125℃; Type: Thick Film Resistor; Tolerance: ±1%; Temperature Coefficient: -</x:v>
       </x:c>
       <x:c r="T11" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R43,R57</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R8; BOM_PASTER_8984112A_Y185.xls: R12</x:v>
       </x:c>
       <x:c r="U11" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V11" s="7" t="str">
-        <x:v>X200T_ECU_B1_V1.0_20240809; legacy_import</x:v>
+        <x:v>legacy_import</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="24" customHeight="1">
       <x:c r="A12" s="7" t="str">
-        <x:v>C106235</x:v>
+        <x:v>C106231</x:v>
       </x:c>
       <x:c r="B12" s="7" t="str">
-        <x:v>RC0402FR-071KL</x:v>
+        <x:v>RC0402FR-070RL</x:v>
       </x:c>
       <x:c r="C12" s="7" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D12" s="7" t="str">
-        <x:v>1kΩ 62.5mW 50V Thick Film Resistor ±100ppm/℃ ±1% 0402 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>0Ω 62.5mW 50V Thick Film Resistor ±1% 0402 Chip Resistor - Surface Mount RoHS</x:v>
       </x:c>
       <x:c r="E12" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F12" s="7" t="str">
-        <x:v>R_1kohm_0402</x:v>
+        <x:v>R_0ohm_0402</x:v>
       </x:c>
       <x:c r="G12" s="7" t="str">
         <x:v>R_0402_1005Metric</x:v>
       </x:c>
       <x:c r="H12" s="7" t="str">
-        <x:v>1kΩ</x:v>
+        <x:v>0Ω</x:v>
       </x:c>
       <x:c r="I12" s="7" t="str">
         <x:v>0402</x:v>
       </x:c>
       <x:c r="J12" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C106235</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C106231</x:v>
       </x:c>
       <x:c r="K12" s="7" t="str"/>
       <x:c r="L12" s="7" t="str"/>
       <x:c r="M12" s="7" t="str">
-        <x:v>../datasheets/C106235/RC0402FR-071KL.pdf</x:v>
+        <x:v>../datasheets/C106231/RC0402FR-070RL.pdf</x:v>
       </x:c>
       <x:c r="N12" s="7" t="str"/>
       <x:c r="O12" s="7" t="str">
@@ -4283,16 +4345,16 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str">
-        <x:v>RC0402FR-071KL</x:v>
+        <x:v>贴片电阻</x:v>
       </x:c>
       <x:c r="R12" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C106235.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C106231.html</x:v>
       </x:c>
       <x:c r="S12" s="7" t="str">
-        <x:v>Package: 0402; Resistance: 1kΩ; Power(Watts): 62.5mW; Voltage Rating: 50V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±1%</x:v>
+        <x:v>Package: 0402; Resistance: 0Ω; Power(Watts): 62.5mW; Voltage Rating: 50V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: -; Tolerance: ±1%</x:v>
       </x:c>
       <x:c r="T12" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R5,R6,R7</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R43,R57</x:v>
       </x:c>
       <x:c r="U12" s="7" t="str">
         <x:v>METADATA_READY</x:v>
@@ -4303,39 +4365,39 @@
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
       <x:c r="A13" s="7" t="str">
-        <x:v>C138031</x:v>
+        <x:v>C106235</x:v>
       </x:c>
       <x:c r="B13" s="7" t="str">
-        <x:v>RC0402FR-0720RL</x:v>
+        <x:v>RC0402FR-071KL</x:v>
       </x:c>
       <x:c r="C13" s="7" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D13" s="7" t="str">
-        <x:v>20Ω 62.5mW 50V Thick Film Resistor ±100ppm/℃ ±1% 0402 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>1kΩ 62.5mW 50V Thick Film Resistor ±100ppm/℃ ±1% 0402 Chip Resistor - Surface Mount RoHS</x:v>
       </x:c>
       <x:c r="E13" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F13" s="7" t="str">
-        <x:v>R_20ohm_0402</x:v>
+        <x:v>R_1kohm_0402</x:v>
       </x:c>
       <x:c r="G13" s="7" t="str">
         <x:v>R_0402_1005Metric</x:v>
       </x:c>
       <x:c r="H13" s="7" t="str">
-        <x:v>20Ω</x:v>
+        <x:v>1kΩ</x:v>
       </x:c>
       <x:c r="I13" s="7" t="str">
         <x:v>0402</x:v>
       </x:c>
       <x:c r="J13" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C138031</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C106235</x:v>
       </x:c>
       <x:c r="K13" s="7" t="str"/>
       <x:c r="L13" s="7" t="str"/>
       <x:c r="M13" s="7" t="str">
-        <x:v>../datasheets/C138031/RC0402FR-0720RL.pdf</x:v>
+        <x:v>../datasheets/C106235/RC0402FR-071KL.pdf</x:v>
       </x:c>
       <x:c r="N13" s="7" t="str"/>
       <x:c r="O13" s="7" t="str">
@@ -4345,59 +4407,59 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q13" s="7" t="str">
-        <x:v>R0402</x:v>
+        <x:v>RC0402FR-071KL</x:v>
       </x:c>
       <x:c r="R13" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C138031.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C106235.html</x:v>
       </x:c>
       <x:c r="S13" s="7" t="str">
-        <x:v>Package: 0402; Resistance: 20Ω; Power(Watts): 62.5mW; Voltage Rating: 50V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±1%</x:v>
+        <x:v>Package: 0402; Resistance: 1kΩ; Power(Watts): 62.5mW; Voltage Rating: 50V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±1%</x:v>
       </x:c>
       <x:c r="T13" s="7" t="str">
-        <x:v>Designators: R8, R9, R10, R19, R20, R21, R22, R23, R24, R26, R35, R36, R37, R47, R48, R49, R83, R86, R87, R88, R89, R90, R94, R95, R98, R100, R101</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R5,R6,R7</x:v>
       </x:c>
       <x:c r="U13" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V13" s="7" t="str">
-        <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
+        <x:v>X200T_ECU_B1_V1.0_20240809; legacy_import</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="24" customHeight="1">
       <x:c r="A14" s="7" t="str">
-        <x:v>C138135</x:v>
+        <x:v>C114761</x:v>
       </x:c>
       <x:c r="B14" s="7" t="str">
-        <x:v>RC0201FR-074K7L</x:v>
+        <x:v>RC0402FR-0715KL</x:v>
       </x:c>
       <x:c r="C14" s="7" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D14" s="7" t="str">
-        <x:v>50mW 4.7kΩ 25V Thick Film Resistor ±1% ±200ppm/℃ 0201 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>15kΩ ±1% 62.5mW 0402 Thick Film Resistor</x:v>
       </x:c>
       <x:c r="E14" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F14" s="7" t="str">
-        <x:v>R_4_7kohm_0201</x:v>
+        <x:v>RC0402FR-0715KL</x:v>
       </x:c>
       <x:c r="G14" s="7" t="str">
-        <x:v>ExternalDriver_RC0201FR-074K7L</x:v>
+        <x:v>R_0402_1005Metric</x:v>
       </x:c>
       <x:c r="H14" s="7" t="str">
-        <x:v>4.7kΩ</x:v>
+        <x:v>15kΩ</x:v>
       </x:c>
       <x:c r="I14" s="7" t="str">
-        <x:v>0201</x:v>
+        <x:v>0402</x:v>
       </x:c>
       <x:c r="J14" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C138135</x:v>
+        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20250610/89E4D743C004A82A45145C7A2CC3A578.pdf</x:v>
       </x:c>
       <x:c r="K14" s="7" t="str"/>
       <x:c r="L14" s="7" t="str"/>
       <x:c r="M14" s="7" t="str">
-        <x:v>../datasheets/C138135/RC0201FR-074K7L.pdf</x:v>
+        <x:v>../datasheets/C114761/RC0402FR-0715KL.pdf</x:v>
       </x:c>
       <x:c r="N14" s="7" t="str"/>
       <x:c r="O14" s="7" t="str">
@@ -4407,121 +4469,121 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str">
-        <x:v>RC0201FR-074K7L</x:v>
+        <x:v>R_0402_1005Metric</x:v>
       </x:c>
       <x:c r="R14" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C138135.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C114761.html</x:v>
       </x:c>
       <x:c r="S14" s="7" t="str">
-        <x:v>Package: 0201; Power(Watts): 50mW; Resistance: 4.7kΩ; Voltage Rating: 25V; Operating Temperature: -55℃~+125℃; Type: Thick Film Resistor; Tolerance: ±1%; Temperature Coefficient: ±200ppm/℃</x:v>
+        <x:v>Package: 0402; Power(Watts): 62.5mW; Resistance: 15kΩ; Voltage Rating: 50V; Type: Thick Film Resistor; Tolerance: ±1%</x:v>
       </x:c>
       <x:c r="T14" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R20,R48; BOM_PASTER_8984112A_Y185.xls: R21</x:v>
+        <x:v>Added 2026-10-04 for LA150C library rebuild; Value uses master electrical value.</x:v>
       </x:c>
       <x:c r="U14" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V14" s="7" t="str">
-        <x:v>legacy_import</x:v>
+        <x:v>LocalParts</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
       <x:c r="A15" s="7" t="str">
-        <x:v>C138139</x:v>
+        <x:v>C138031</x:v>
       </x:c>
       <x:c r="B15" s="7" t="str">
-        <x:v>RC0201FR-0747KL</x:v>
+        <x:v>RC0402FR-0720RL</x:v>
       </x:c>
       <x:c r="C15" s="7" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D15" s="7" t="str">
-        <x:v>50mW 47kΩ 25V Thick Film Resistor ±1% ±200ppm/℃ 0201 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>20Ω 62.5mW 50V Thick Film Resistor ±100ppm/℃ ±1% 0402 Chip Resistor - Surface Mount RoHS</x:v>
       </x:c>
       <x:c r="E15" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F15" s="7" t="str">
-        <x:v>R_47kohm_0201</x:v>
+        <x:v>R_20ohm_0402</x:v>
       </x:c>
       <x:c r="G15" s="7" t="str">
-        <x:v>ExternalDriver_RC0201FR-0747KL</x:v>
+        <x:v>R_0402_1005Metric</x:v>
       </x:c>
       <x:c r="H15" s="7" t="str">
-        <x:v>47kΩ</x:v>
+        <x:v>20Ω</x:v>
       </x:c>
       <x:c r="I15" s="7" t="str">
-        <x:v>0201</x:v>
+        <x:v>0402</x:v>
       </x:c>
       <x:c r="J15" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C138139</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C138031</x:v>
       </x:c>
       <x:c r="K15" s="7" t="str"/>
       <x:c r="L15" s="7" t="str"/>
       <x:c r="M15" s="7" t="str">
-        <x:v>../datasheets/C138139/RC0201FR-0747KL.pdf</x:v>
+        <x:v>../datasheets/C138031/RC0402FR-0720RL.pdf</x:v>
       </x:c>
       <x:c r="N15" s="7" t="str"/>
       <x:c r="O15" s="7" t="str">
-        <x:v>OutOfStock</x:v>
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="P15" s="7" t="str">
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q15" s="7" t="str">
-        <x:v>RC0201FR-0747KL</x:v>
+        <x:v>R0402</x:v>
       </x:c>
       <x:c r="R15" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C138139.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C138031.html</x:v>
       </x:c>
       <x:c r="S15" s="7" t="str">
-        <x:v>Package: 0201; Power(Watts): 50mW; Resistance: 47kΩ; Voltage Rating: 25V; Operating Temperature: -55℃~+125℃; Type: Thick Film Resistor; Tolerance: ±1%; Temperature Coefficient: ±200ppm/℃</x:v>
+        <x:v>Package: 0402; Resistance: 20Ω; Power(Watts): 62.5mW; Voltage Rating: 50V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±1%</x:v>
       </x:c>
       <x:c r="T15" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R15,R18; BOM_PASTER_8984112A_Y185.xls: R8</x:v>
+        <x:v>Designators: R8, R9, R10, R19, R20, R21, R22, R23, R24, R26, R35, R36, R37, R47, R48, R49, R83, R86, R87, R88, R89, R90, R94, R95, R98, R100, R101</x:v>
       </x:c>
       <x:c r="U15" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V15" s="7" t="str">
-        <x:v>legacy_import</x:v>
+        <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="24" customHeight="1">
       <x:c r="A16" s="7" t="str">
-        <x:v>C138165</x:v>
+        <x:v>C138135</x:v>
       </x:c>
       <x:c r="B16" s="7" t="str">
-        <x:v>RC0201FR-071KL</x:v>
+        <x:v>RC0201FR-074K7L</x:v>
       </x:c>
       <x:c r="C16" s="7" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D16" s="7" t="str">
-        <x:v>50mW 1kΩ 25V Thick Film Resistor ±1% ±200ppm/℃ 0201 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>50mW 4.7kΩ 25V Thick Film Resistor ±1% ±200ppm/℃ 0201 Chip Resistor - Surface Mount RoHS</x:v>
       </x:c>
       <x:c r="E16" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F16" s="7" t="str">
-        <x:v>R_1kohm_0201</x:v>
+        <x:v>R_4_7kohm_0201</x:v>
       </x:c>
       <x:c r="G16" s="7" t="str">
-        <x:v>ExternalDriver_RC0201FR-071KL</x:v>
+        <x:v>ExternalDriver_RC0201FR-074K7L</x:v>
       </x:c>
       <x:c r="H16" s="7" t="str">
-        <x:v>1kΩ</x:v>
+        <x:v>4.7kΩ</x:v>
       </x:c>
       <x:c r="I16" s="7" t="str">
         <x:v>0201</x:v>
       </x:c>
       <x:c r="J16" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C138165</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C138135</x:v>
       </x:c>
       <x:c r="K16" s="7" t="str"/>
       <x:c r="L16" s="7" t="str"/>
       <x:c r="M16" s="7" t="str">
-        <x:v>../datasheets/C138165/RC0201FR-071KL.pdf</x:v>
+        <x:v>../datasheets/C138135/RC0201FR-074K7L.pdf</x:v>
       </x:c>
       <x:c r="N16" s="7" t="str"/>
       <x:c r="O16" s="7" t="str">
@@ -4531,16 +4593,16 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q16" s="7" t="str">
-        <x:v>RC0201FR-071KL</x:v>
+        <x:v>RC0201FR-074K7L</x:v>
       </x:c>
       <x:c r="R16" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C138165.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C138135.html</x:v>
       </x:c>
       <x:c r="S16" s="7" t="str">
-        <x:v>Package: 0201; Power(Watts): 50mW; Resistance: 1kΩ; Voltage Rating: 25V; Operating Temperature: -55℃~+125℃; Type: Thick Film Resistor; Tolerance: ±1%; Temperature Coefficient: ±200ppm/℃</x:v>
+        <x:v>Package: 0201; Power(Watts): 50mW; Resistance: 4.7kΩ; Voltage Rating: 25V; Operating Temperature: -55℃~+125℃; Type: Thick Film Resistor; Tolerance: ±1%; Temperature Coefficient: ±200ppm/℃</x:v>
       </x:c>
       <x:c r="T16" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls, BOM_PASTER_8984112A_Y189.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R35,R36; BOM_PASTER_8984112A_Y185.xls: R23; BOM_PASTER_8984112A_Y189.xls: R1</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R20,R48; BOM_PASTER_8984112A_Y185.xls: R21</x:v>
       </x:c>
       <x:c r="U16" s="7" t="str">
         <x:v>METADATA_READY</x:v>
@@ -4551,101 +4613,101 @@
     </x:row>
     <x:row r="17" ht="24" customHeight="1">
       <x:c r="A17" s="7" t="str">
-        <x:v>C144651</x:v>
+        <x:v>C138139</x:v>
       </x:c>
       <x:c r="B17" s="7" t="str">
-        <x:v>AC0603FR-074R7L</x:v>
+        <x:v>RC0201FR-0747KL</x:v>
       </x:c>
       <x:c r="C17" s="7" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D17" s="7" t="str">
-        <x:v>4.7Ω 100mW 75V Thick Film Resistor ±1% ±200ppm/℃ 0603 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>50mW 47kΩ 25V Thick Film Resistor ±1% ±200ppm/℃ 0201 Chip Resistor - Surface Mount RoHS</x:v>
       </x:c>
       <x:c r="E17" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F17" s="7" t="str">
-        <x:v>R_4_7ohm_0603</x:v>
+        <x:v>R_47kohm_0201</x:v>
       </x:c>
       <x:c r="G17" s="7" t="str">
-        <x:v>R_0603_1608Metric</x:v>
+        <x:v>ExternalDriver_RC0201FR-0747KL</x:v>
       </x:c>
       <x:c r="H17" s="7" t="str">
-        <x:v>4.7Ω</x:v>
+        <x:v>47kΩ</x:v>
       </x:c>
       <x:c r="I17" s="7" t="str">
-        <x:v>0603</x:v>
+        <x:v>0201</x:v>
       </x:c>
       <x:c r="J17" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/3511efb0564cb1711d9237ab09d6e97b.pdf?productCode=C144651</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C138139</x:v>
       </x:c>
       <x:c r="K17" s="7" t="str"/>
       <x:c r="L17" s="7" t="str"/>
       <x:c r="M17" s="7" t="str">
-        <x:v>../datasheets/C144651/AC0603FR-074R7L.pdf</x:v>
+        <x:v>../datasheets/C138139/RC0201FR-0747KL.pdf</x:v>
       </x:c>
       <x:c r="N17" s="7" t="str"/>
       <x:c r="O17" s="7" t="str">
-        <x:v>Active</x:v>
+        <x:v>OutOfStock</x:v>
       </x:c>
       <x:c r="P17" s="7" t="str">
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q17" s="7" t="str">
-        <x:v>R0603</x:v>
+        <x:v>RC0201FR-0747KL</x:v>
       </x:c>
       <x:c r="R17" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C144651.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C138139.html</x:v>
       </x:c>
       <x:c r="S17" s="7" t="str">
-        <x:v>Package: 0603; Resistance: 4.7Ω; Power(Watts): 100mW; Voltage Rating: 75V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Tolerance: ±1%; Temperature Coefficient: ±200ppm/℃</x:v>
+        <x:v>Package: 0201; Power(Watts): 50mW; Resistance: 47kΩ; Voltage Rating: 25V; Operating Temperature: -55℃~+125℃; Type: Thick Film Resistor; Tolerance: ±1%; Temperature Coefficient: ±200ppm/℃</x:v>
       </x:c>
       <x:c r="T17" s="7" t="str">
-        <x:v>Designators: R32, R33, R34, R44, R45, R46</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R15,R18; BOM_PASTER_8984112A_Y185.xls: R8</x:v>
       </x:c>
       <x:c r="U17" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V17" s="7" t="str">
-        <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
+        <x:v>legacy_import</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="24" customHeight="1">
       <x:c r="A18" s="7" t="str">
-        <x:v>C14675</x:v>
+        <x:v>C138165</x:v>
       </x:c>
       <x:c r="B18" s="7" t="str">
-        <x:v>RC0603FR-07100KL</x:v>
+        <x:v>RC0201FR-071KL</x:v>
       </x:c>
       <x:c r="C18" s="7" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D18" s="7" t="str">
-        <x:v>100mW 100kΩ 75V Thick Film Resistor ±100ppm/℃ ±1% 0603 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>50mW 1kΩ 25V Thick Film Resistor ±1% ±200ppm/℃ 0201 Chip Resistor - Surface Mount RoHS</x:v>
       </x:c>
       <x:c r="E18" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F18" s="7" t="str">
-        <x:v>R_100kohm_0603</x:v>
+        <x:v>R_1kohm_0201</x:v>
       </x:c>
       <x:c r="G18" s="7" t="str">
-        <x:v>R_0603_1608Metric</x:v>
+        <x:v>ExternalDriver_RC0201FR-071KL</x:v>
       </x:c>
       <x:c r="H18" s="7" t="str">
-        <x:v>100kΩ</x:v>
+        <x:v>1kΩ</x:v>
       </x:c>
       <x:c r="I18" s="7" t="str">
-        <x:v>0603</x:v>
+        <x:v>0201</x:v>
       </x:c>
       <x:c r="J18" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C14675</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C138165</x:v>
       </x:c>
       <x:c r="K18" s="7" t="str"/>
       <x:c r="L18" s="7" t="str"/>
       <x:c r="M18" s="7" t="str">
-        <x:v>../datasheets/C14675/RC0603FR-07100KL.pdf</x:v>
+        <x:v>../datasheets/C138165/RC0201FR-071KL.pdf</x:v>
       </x:c>
       <x:c r="N18" s="7" t="str"/>
       <x:c r="O18" s="7" t="str">
@@ -4655,59 +4717,59 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q18" s="7" t="str">
-        <x:v>R0603</x:v>
+        <x:v>RC0201FR-071KL</x:v>
       </x:c>
       <x:c r="R18" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C14675.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C138165.html</x:v>
       </x:c>
       <x:c r="S18" s="7" t="str">
-        <x:v>Package: 0603; Power(Watts): 100mW; Resistance: 100kΩ; Voltage Rating: 75V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±1%</x:v>
+        <x:v>Package: 0201; Power(Watts): 50mW; Resistance: 1kΩ; Voltage Rating: 25V; Operating Temperature: -55℃~+125℃; Type: Thick Film Resistor; Tolerance: ±1%; Temperature Coefficient: ±200ppm/℃</x:v>
       </x:c>
       <x:c r="T18" s="7" t="str">
-        <x:v>Designators: R68</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls, BOM_PASTER_8984112A_Y189.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R35,R36; BOM_PASTER_8984112A_Y185.xls: R23; BOM_PASTER_8984112A_Y189.xls: R1</x:v>
       </x:c>
       <x:c r="U18" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V18" s="7" t="str">
-        <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
+        <x:v>legacy_import</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="24" customHeight="1">
       <x:c r="A19" s="7" t="str">
-        <x:v>C163437</x:v>
+        <x:v>C144651</x:v>
       </x:c>
       <x:c r="B19" s="7" t="str">
-        <x:v>RC0402JR-0762RL</x:v>
+        <x:v>AC0603FR-074R7L</x:v>
       </x:c>
       <x:c r="C19" s="7" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D19" s="7" t="str">
-        <x:v>62Ω 62.5mW 50V Thick Film Resistor ±100ppm/℃ ±5% 0402 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>4.7Ω 100mW 75V Thick Film Resistor ±1% ±200ppm/℃ 0603 Chip Resistor - Surface Mount RoHS</x:v>
       </x:c>
       <x:c r="E19" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F19" s="7" t="str">
-        <x:v>R_62ohm_0402</x:v>
+        <x:v>R_4_7ohm_0603</x:v>
       </x:c>
       <x:c r="G19" s="7" t="str">
-        <x:v>R_0402_1005Metric</x:v>
+        <x:v>R_0603_1608Metric</x:v>
       </x:c>
       <x:c r="H19" s="7" t="str">
-        <x:v>62Ω</x:v>
+        <x:v>4.7Ω</x:v>
       </x:c>
       <x:c r="I19" s="7" t="str">
-        <x:v>0402</x:v>
+        <x:v>0603</x:v>
       </x:c>
       <x:c r="J19" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C163437</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/3511efb0564cb1711d9237ab09d6e97b.pdf?productCode=C144651</x:v>
       </x:c>
       <x:c r="K19" s="7" t="str"/>
       <x:c r="L19" s="7" t="str"/>
       <x:c r="M19" s="7" t="str">
-        <x:v>../datasheets/C163437/RC0402JR-0762RL.pdf</x:v>
+        <x:v>../datasheets/C144651/AC0603FR-074R7L.pdf</x:v>
       </x:c>
       <x:c r="N19" s="7" t="str"/>
       <x:c r="O19" s="7" t="str">
@@ -4717,16 +4779,16 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q19" s="7" t="str">
-        <x:v>R0402</x:v>
+        <x:v>R0603</x:v>
       </x:c>
       <x:c r="R19" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C163437.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C144651.html</x:v>
       </x:c>
       <x:c r="S19" s="7" t="str">
-        <x:v>Package: 0402; Resistance: 62Ω; Power(Watts): 62.5mW; Voltage Rating: 50V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±5%</x:v>
+        <x:v>Package: 0603; Resistance: 4.7Ω; Power(Watts): 100mW; Voltage Rating: 75V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Tolerance: ±1%; Temperature Coefficient: ±200ppm/℃</x:v>
       </x:c>
       <x:c r="T19" s="7" t="str">
-        <x:v>Designators: R13, R14, R96, R97</x:v>
+        <x:v>Designators: R32, R33, R34, R44, R45, R46</x:v>
       </x:c>
       <x:c r="U19" s="7" t="str">
         <x:v>METADATA_READY</x:v>
@@ -4737,35 +4799,39 @@
     </x:row>
     <x:row r="20" ht="24" customHeight="1">
       <x:c r="A20" s="7" t="str">
-        <x:v>C25744</x:v>
+        <x:v>C14675</x:v>
       </x:c>
       <x:c r="B20" s="7" t="str">
-        <x:v>0402WGF1002TCE</x:v>
+        <x:v>RC0603FR-07100KL</x:v>
       </x:c>
       <x:c r="C20" s="7" t="str">
-        <x:v>UNI-ROYAL</x:v>
+        <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D20" s="7" t="str">
-        <x:v>10kΩ ±1% 62.5mW Thick Film Resistor</x:v>
+        <x:v>100mW 100kΩ 75V Thick Film Resistor ±100ppm/℃ ±1% 0603 Chip Resistor - Surface Mount RoHS</x:v>
       </x:c>
       <x:c r="E20" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
-      <x:c r="F20" s="7" t="str"/>
-      <x:c r="G20" s="7" t="str"/>
+      <x:c r="F20" s="7" t="str">
+        <x:v>R_100kohm_0603</x:v>
+      </x:c>
+      <x:c r="G20" s="7" t="str">
+        <x:v>R_0603_1608Metric</x:v>
+      </x:c>
       <x:c r="H20" s="7" t="str">
-        <x:v>10kΩ</x:v>
+        <x:v>100kΩ</x:v>
       </x:c>
       <x:c r="I20" s="7" t="str">
-        <x:v>0402</x:v>
+        <x:v>0603</x:v>
       </x:c>
       <x:c r="J20" s="7" t="str">
-        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20200306/C422600_1E6D84923E4A46A82E41ADD87F860B5C.pdf</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C14675</x:v>
       </x:c>
       <x:c r="K20" s="7" t="str"/>
       <x:c r="L20" s="7" t="str"/>
       <x:c r="M20" s="7" t="str">
-        <x:v>../datasheets/C25744/0402WGF1002TCE.pdf</x:v>
+        <x:v>../datasheets/C14675/RC0603FR-07100KL.pdf</x:v>
       </x:c>
       <x:c r="N20" s="7" t="str"/>
       <x:c r="O20" s="7" t="str">
@@ -4775,59 +4841,59 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q20" s="7" t="str">
-        <x:v>0402-10K-1%</x:v>
+        <x:v>R0603</x:v>
       </x:c>
       <x:c r="R20" s="7" t="str">
-        <x:v>https://item.szlcsc.com/26487.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C14675.html</x:v>
       </x:c>
       <x:c r="S20" s="7" t="str">
-        <x:v>Package: 0402; Resistance: 10kΩ; Tolerance: ±1%; Power: 62.5mW</x:v>
+        <x:v>Package: 0603; Power(Watts): 100mW; Resistance: 100kΩ; Voltage Rating: 75V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±1%</x:v>
       </x:c>
       <x:c r="T20" s="7" t="str">
-        <x:v>Designators: Y43-R3,R4,R5,R6,R7</x:v>
+        <x:v>Designators: R68</x:v>
       </x:c>
       <x:c r="U20" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V20" s="7" t="str">
-        <x:v>Y43</x:v>
+        <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="24" customHeight="1">
       <x:c r="A21" s="7" t="str">
-        <x:v>C273722</x:v>
+        <x:v>C163437</x:v>
       </x:c>
       <x:c r="B21" s="7" t="str">
-        <x:v>RC0402FR-07768KL</x:v>
+        <x:v>RC0402JR-0762RL</x:v>
       </x:c>
       <x:c r="C21" s="7" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D21" s="7" t="str">
-        <x:v>768kΩ 62.5mW 50V Thick Film Resistor ±100ppm/℃ ±1% 0402 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>62Ω 62.5mW 50V Thick Film Resistor ±100ppm/℃ ±5% 0402 Chip Resistor - Surface Mount RoHS</x:v>
       </x:c>
       <x:c r="E21" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F21" s="7" t="str">
-        <x:v>R_768kohm_0402</x:v>
+        <x:v>R_62ohm_0402</x:v>
       </x:c>
       <x:c r="G21" s="7" t="str">
         <x:v>R_0402_1005Metric</x:v>
       </x:c>
       <x:c r="H21" s="7" t="str">
-        <x:v>768kΩ</x:v>
+        <x:v>62Ω</x:v>
       </x:c>
       <x:c r="I21" s="7" t="str">
         <x:v>0402</x:v>
       </x:c>
       <x:c r="J21" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C273722</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C163437</x:v>
       </x:c>
       <x:c r="K21" s="7" t="str"/>
       <x:c r="L21" s="7" t="str"/>
       <x:c r="M21" s="7" t="str">
-        <x:v>../datasheets/C273722/RC0402FR-07768KL.pdf</x:v>
+        <x:v>../datasheets/C163437/RC0402JR-0762RL.pdf</x:v>
       </x:c>
       <x:c r="N21" s="7" t="str"/>
       <x:c r="O21" s="7" t="str">
@@ -4840,13 +4906,13 @@
         <x:v>R0402</x:v>
       </x:c>
       <x:c r="R21" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C273722.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C163437.html</x:v>
       </x:c>
       <x:c r="S21" s="7" t="str">
-        <x:v>Package: 0402; Resistance: 768kΩ; Power(Watts): 62.5mW; Voltage Rating: 50V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±1%</x:v>
+        <x:v>Package: 0402; Resistance: 62Ω; Power(Watts): 62.5mW; Voltage Rating: 50V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±5%</x:v>
       </x:c>
       <x:c r="T21" s="7" t="str">
-        <x:v>Designators: R2</x:v>
+        <x:v>Designators: R13, R14, R96, R97</x:v>
       </x:c>
       <x:c r="U21" s="7" t="str">
         <x:v>METADATA_READY</x:v>
@@ -4857,39 +4923,35 @@
     </x:row>
     <x:row r="22" ht="24" customHeight="1">
       <x:c r="A22" s="7" t="str">
-        <x:v>C274877</x:v>
+        <x:v>C25744</x:v>
       </x:c>
       <x:c r="B22" s="7" t="str">
-        <x:v>RC0201FR-076K8L</x:v>
+        <x:v>0402WGF1002TCE</x:v>
       </x:c>
       <x:c r="C22" s="7" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>UNI-ROYAL</x:v>
       </x:c>
       <x:c r="D22" s="7" t="str">
-        <x:v>50mW 6.8kΩ 25V Thick Film Resistor ±1% ±200ppm/℃ 0201 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>10kΩ ±1% 62.5mW Thick Film Resistor</x:v>
       </x:c>
       <x:c r="E22" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
-      <x:c r="F22" s="7" t="str">
-        <x:v>R_6_8kohm_0201</x:v>
-      </x:c>
-      <x:c r="G22" s="7" t="str">
-        <x:v>ExternalDriver_RC0201FR-076K8L</x:v>
-      </x:c>
+      <x:c r="F22" s="7" t="str"/>
+      <x:c r="G22" s="7" t="str"/>
       <x:c r="H22" s="7" t="str">
-        <x:v>6.8kΩ</x:v>
+        <x:v>10kΩ</x:v>
       </x:c>
       <x:c r="I22" s="7" t="str">
-        <x:v>0201</x:v>
+        <x:v>0402</x:v>
       </x:c>
       <x:c r="J22" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C274877</x:v>
+        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20200306/C422600_1E6D84923E4A46A82E41ADD87F860B5C.pdf</x:v>
       </x:c>
       <x:c r="K22" s="7" t="str"/>
       <x:c r="L22" s="7" t="str"/>
       <x:c r="M22" s="7" t="str">
-        <x:v>../datasheets/C274877/RC0201FR-076K8L.pdf</x:v>
+        <x:v>../datasheets/C25744/0402WGF1002TCE.pdf</x:v>
       </x:c>
       <x:c r="N22" s="7" t="str"/>
       <x:c r="O22" s="7" t="str">
@@ -4899,121 +4961,121 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q22" s="7" t="str">
-        <x:v>RC0201FR-076K8L</x:v>
+        <x:v>0402-10K-1%</x:v>
       </x:c>
       <x:c r="R22" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C274877.html</x:v>
+        <x:v>https://item.szlcsc.com/26487.html</x:v>
       </x:c>
       <x:c r="S22" s="7" t="str">
-        <x:v>Package: 0201; Power(Watts): 50mW; Resistance: 6.8kΩ; Voltage Rating: 25V; Operating Temperature: -55℃~+125℃; Type: Thick Film Resistor; Tolerance: ±1%; Temperature Coefficient: ±200ppm/℃</x:v>
+        <x:v>Package: 0402; Resistance: 10kΩ; Tolerance: ±1%; Power: 62.5mW</x:v>
       </x:c>
       <x:c r="T22" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R13,R47; BOM_PASTER_8984112A_Y185.xls: R17</x:v>
+        <x:v>Designators: Y43-R3,R4,R5,R6,R7</x:v>
       </x:c>
       <x:c r="U22" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V22" s="7" t="str">
-        <x:v>legacy_import</x:v>
+        <x:v>Y43</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="24" customHeight="1">
       <x:c r="A23" s="7" t="str">
-        <x:v>C474825</x:v>
+        <x:v>C273722</x:v>
       </x:c>
       <x:c r="B23" s="7" t="str">
-        <x:v>RC0201FR-0776K8L</x:v>
+        <x:v>RC0402FR-07768KL</x:v>
       </x:c>
       <x:c r="C23" s="7" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D23" s="7" t="str">
-        <x:v>50mW 76.8kΩ 25V Thick Film Resistor ±1% ±200ppm/℃ 0201 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>768kΩ 62.5mW 50V Thick Film Resistor ±100ppm/℃ ±1% 0402 Chip Resistor - Surface Mount RoHS</x:v>
       </x:c>
       <x:c r="E23" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F23" s="7" t="str">
-        <x:v>R_76_8kohm_0201</x:v>
+        <x:v>R_768kohm_0402</x:v>
       </x:c>
       <x:c r="G23" s="7" t="str">
-        <x:v>ExternalDriver_RC0201FR-0776K8L</x:v>
+        <x:v>R_0402_1005Metric</x:v>
       </x:c>
       <x:c r="H23" s="7" t="str">
-        <x:v>76.8kΩ</x:v>
+        <x:v>768kΩ</x:v>
       </x:c>
       <x:c r="I23" s="7" t="str">
-        <x:v>0201</x:v>
+        <x:v>0402</x:v>
       </x:c>
       <x:c r="J23" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C474825</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C273722</x:v>
       </x:c>
       <x:c r="K23" s="7" t="str"/>
       <x:c r="L23" s="7" t="str"/>
       <x:c r="M23" s="7" t="str">
-        <x:v>../datasheets/C474825/RC0201FR-0776K8L.pdf</x:v>
+        <x:v>../datasheets/C273722/RC0402FR-07768KL.pdf</x:v>
       </x:c>
       <x:c r="N23" s="7" t="str"/>
       <x:c r="O23" s="7" t="str">
-        <x:v>OutOfStock</x:v>
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="P23" s="7" t="str">
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q23" s="7" t="str">
-        <x:v>RC0201FR-0776K8L</x:v>
+        <x:v>R0402</x:v>
       </x:c>
       <x:c r="R23" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C474825.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C273722.html</x:v>
       </x:c>
       <x:c r="S23" s="7" t="str">
-        <x:v>Package: 0201; Power(Watts): 50mW; Resistance: 76.8kΩ; Voltage Rating: 25V; Operating Temperature: -55℃~+125℃; Type: Thick Film Resistor; Tolerance: ±1%; Temperature Coefficient: ±200ppm/℃</x:v>
+        <x:v>Package: 0402; Resistance: 768kΩ; Power(Watts): 62.5mW; Voltage Rating: 50V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±1%</x:v>
       </x:c>
       <x:c r="T23" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R17</x:v>
+        <x:v>Designators: R2</x:v>
       </x:c>
       <x:c r="U23" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V23" s="7" t="str">
-        <x:v>legacy_import</x:v>
+        <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="24" customHeight="1">
       <x:c r="A24" s="7" t="str">
-        <x:v>C60490</x:v>
+        <x:v>C274877</x:v>
       </x:c>
       <x:c r="B24" s="7" t="str">
-        <x:v>RC0402FR-0710KL</x:v>
+        <x:v>RC0201FR-076K8L</x:v>
       </x:c>
       <x:c r="C24" s="7" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D24" s="7" t="str">
-        <x:v>62.5mW 10kΩ 50V Thick Film Resistor ±100ppm/℃ ±1% 0402 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>50mW 6.8kΩ 25V Thick Film Resistor ±1% ±200ppm/℃ 0201 Chip Resistor - Surface Mount RoHS</x:v>
       </x:c>
       <x:c r="E24" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F24" s="7" t="str">
-        <x:v>R_10kohm_0402</x:v>
+        <x:v>R_6_8kohm_0201</x:v>
       </x:c>
       <x:c r="G24" s="7" t="str">
-        <x:v>R_0402_1005Metric</x:v>
+        <x:v>ExternalDriver_RC0201FR-076K8L</x:v>
       </x:c>
       <x:c r="H24" s="7" t="str">
-        <x:v>10kΩ</x:v>
+        <x:v>6.8kΩ</x:v>
       </x:c>
       <x:c r="I24" s="7" t="str">
-        <x:v>0402</x:v>
+        <x:v>0201</x:v>
       </x:c>
       <x:c r="J24" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C60490</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C274877</x:v>
       </x:c>
       <x:c r="K24" s="7" t="str"/>
       <x:c r="L24" s="7" t="str"/>
       <x:c r="M24" s="7" t="str">
-        <x:v>../datasheets/C60490/RC0402FR-0710KL.pdf</x:v>
+        <x:v>../datasheets/C274877/RC0201FR-076K8L.pdf</x:v>
       </x:c>
       <x:c r="N24" s="7" t="str"/>
       <x:c r="O24" s="7" t="str">
@@ -5023,59 +5085,59 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q24" s="7" t="str">
-        <x:v>R0402</x:v>
+        <x:v>RC0201FR-076K8L</x:v>
       </x:c>
       <x:c r="R24" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C60490.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C274877.html</x:v>
       </x:c>
       <x:c r="S24" s="7" t="str">
-        <x:v>Package: 0402; Power(Watts): 62.5mW; Resistance: 10kΩ; Voltage Rating: 50V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±1%</x:v>
+        <x:v>Package: 0201; Power(Watts): 50mW; Resistance: 6.8kΩ; Voltage Rating: 25V; Operating Temperature: -55℃~+125℃; Type: Thick Film Resistor; Tolerance: ±1%; Temperature Coefficient: ±200ppm/℃</x:v>
       </x:c>
       <x:c r="T24" s="7" t="str">
-        <x:v>Designators: R7, R16, R17, R18, R27, R28, R29, R30, R59, R60, R61, R71, R72, R73, R77, R78, R91, R92, R93, R99</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R13,R47; BOM_PASTER_8984112A_Y185.xls: R17</x:v>
       </x:c>
       <x:c r="U24" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V24" s="7" t="str">
-        <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
+        <x:v>legacy_import</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="24" customHeight="1">
       <x:c r="A25" s="7" t="str">
-        <x:v>C60491</x:v>
+        <x:v>C327379</x:v>
       </x:c>
       <x:c r="B25" s="7" t="str">
-        <x:v>RC0402FR-07100KL</x:v>
+        <x:v>RC0201FR-078K06L</x:v>
       </x:c>
       <x:c r="C25" s="7" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>YAGEO(国巨)</x:v>
       </x:c>
       <x:c r="D25" s="7" t="str">
-        <x:v>100kΩ 62.5mW 50V Thick Film Resistor ±100ppm/℃ ±1% 0402 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>8.06k 1% 0201 chip resistor</x:v>
       </x:c>
       <x:c r="E25" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F25" s="7" t="str">
-        <x:v>R_100kohm_0402</x:v>
+        <x:v>R_8_06k_0201</x:v>
       </x:c>
       <x:c r="G25" s="7" t="str">
-        <x:v>R_0402_1005Metric</x:v>
+        <x:v>R_0201_0603Metric</x:v>
       </x:c>
       <x:c r="H25" s="7" t="str">
-        <x:v>100kΩ</x:v>
+        <x:v>8.06k</x:v>
       </x:c>
       <x:c r="I25" s="7" t="str">
-        <x:v>0402</x:v>
+        <x:v>0201</x:v>
       </x:c>
       <x:c r="J25" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C60491</x:v>
+        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20250610/89E4D743C004A82A45145C7A2CC3A578.pdf</x:v>
       </x:c>
       <x:c r="K25" s="7" t="str"/>
       <x:c r="L25" s="7" t="str"/>
       <x:c r="M25" s="7" t="str">
-        <x:v>../datasheets/C60491/RC0402FR-07100KL.pdf</x:v>
+        <x:v>../datasheets/C327379/RC0201FR-078K06L.pdf</x:v>
       </x:c>
       <x:c r="N25" s="7" t="str"/>
       <x:c r="O25" s="7" t="str">
@@ -5085,121 +5147,121 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q25" s="7" t="str">
-        <x:v>RC0402FR-07100KL</x:v>
+        <x:v>R0201</x:v>
       </x:c>
       <x:c r="R25" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C60491.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C327379.html</x:v>
       </x:c>
       <x:c r="S25" s="7" t="str">
-        <x:v>Package: 0402; Resistance: 100kΩ; Power(Watts): 62.5mW; Voltage Rating: 50V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±1%</x:v>
+        <x:v>Package: 0201; Resistance: 8.06k; Tolerance: 1%</x:v>
       </x:c>
       <x:c r="T25" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R14,R19; BOM_PASTER_8984112A_Y185.xls: R19</x:v>
+        <x:v>EBOM BOM_QS01_GD32F503_V1.10; designators R6/R7/R8/R14/R15/R16.</x:v>
       </x:c>
       <x:c r="U25" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V25" s="7" t="str">
-        <x:v>X200T_ECU_B1_V1.0_20240809; legacy_import</x:v>
+        <x:v>EBOM_V1.10</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="24" customHeight="1">
       <x:c r="A26" s="7" t="str">
-        <x:v>C723375</x:v>
+        <x:v>C474825</x:v>
       </x:c>
       <x:c r="B26" s="7" t="str">
-        <x:v>PA2512FKF7T0R003E</x:v>
+        <x:v>RC0201FR-0776K8L</x:v>
       </x:c>
       <x:c r="C26" s="7" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D26" s="7" t="str">
-        <x:v>3mΩ ±1% 3W Current Sense Resistor</x:v>
+        <x:v>50mW 76.8kΩ 25V Thick Film Resistor ±1% ±200ppm/℃ 0201 Chip Resistor - Surface Mount RoHS</x:v>
       </x:c>
       <x:c r="E26" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F26" s="7" t="str">
-        <x:v>R_3mohm_2512</x:v>
+        <x:v>R_76_8kohm_0201</x:v>
       </x:c>
       <x:c r="G26" s="7" t="str">
-        <x:v>R_2512_6332Metric</x:v>
+        <x:v>ExternalDriver_RC0201FR-0776K8L</x:v>
       </x:c>
       <x:c r="H26" s="7" t="str">
-        <x:v>3mΩ</x:v>
+        <x:v>76.8kΩ</x:v>
       </x:c>
       <x:c r="I26" s="7" t="str">
-        <x:v>2512</x:v>
+        <x:v>0201</x:v>
       </x:c>
       <x:c r="J26" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/5b6b15592a49e0e574b8071c20ab494b.pdf?productCode=C723375</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C474825</x:v>
       </x:c>
       <x:c r="K26" s="7" t="str"/>
       <x:c r="L26" s="7" t="str"/>
       <x:c r="M26" s="7" t="str">
-        <x:v>../datasheets/C723375/PA2512FKF7T0R003E.pdf</x:v>
+        <x:v>../datasheets/C474825/RC0201FR-0776K8L.pdf</x:v>
       </x:c>
       <x:c r="N26" s="7" t="str"/>
       <x:c r="O26" s="7" t="str">
-        <x:v>Active</x:v>
+        <x:v>OutOfStock</x:v>
       </x:c>
       <x:c r="P26" s="7" t="str">
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q26" s="7" t="str">
-        <x:v>R2512</x:v>
+        <x:v>RC0201FR-0776K8L</x:v>
       </x:c>
       <x:c r="R26" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C723375.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C474825.html</x:v>
       </x:c>
       <x:c r="S26" s="7" t="str">
-        <x:v>Package: 2512; Power(Watts): 3W; Resistance: 3mΩ; Voltage Rating: -; Type: Current Sense Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±1%</x:v>
+        <x:v>Package: 0201; Power(Watts): 50mW; Resistance: 76.8kΩ; Voltage Rating: 25V; Operating Temperature: -55℃~+125℃; Type: Thick Film Resistor; Tolerance: ±1%; Temperature Coefficient: ±200ppm/℃</x:v>
       </x:c>
       <x:c r="T26" s="7" t="str">
-        <x:v>Designators: R62, R63, R64</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R17</x:v>
       </x:c>
       <x:c r="U26" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V26" s="7" t="str">
-        <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
+        <x:v>legacy_import</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="24" customHeight="1">
       <x:c r="A27" s="7" t="str">
-        <x:v>C77623</x:v>
+        <x:v>C60490</x:v>
       </x:c>
       <x:c r="B27" s="7" t="str">
-        <x:v>RC0201FR-07100RL</x:v>
+        <x:v>RC0402FR-0710KL</x:v>
       </x:c>
       <x:c r="C27" s="7" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D27" s="7" t="str">
-        <x:v>50mW 100Ω 25V Thick Film Resistor ±1% ±200ppm/℃ 0201 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>62.5mW 10kΩ 50V Thick Film Resistor ±100ppm/℃ ±1% 0402 Chip Resistor - Surface Mount RoHS</x:v>
       </x:c>
       <x:c r="E27" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F27" s="7" t="str">
-        <x:v>R_100ohm_0201</x:v>
+        <x:v>R_10kohm_0402</x:v>
       </x:c>
       <x:c r="G27" s="7" t="str">
-        <x:v>ExternalDriver_RC0201FR-07100RL</x:v>
+        <x:v>R_0402_1005Metric</x:v>
       </x:c>
       <x:c r="H27" s="7" t="str">
-        <x:v>100Ω</x:v>
+        <x:v>10kΩ</x:v>
       </x:c>
       <x:c r="I27" s="7" t="str">
-        <x:v>0201</x:v>
+        <x:v>0402</x:v>
       </x:c>
       <x:c r="J27" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C77623</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C60490</x:v>
       </x:c>
       <x:c r="K27" s="7" t="str"/>
       <x:c r="L27" s="7" t="str"/>
       <x:c r="M27" s="7" t="str">
-        <x:v>../datasheets/C77623/RC0201FR-07100RL.pdf</x:v>
+        <x:v>../datasheets/C60490/RC0402FR-0710KL.pdf</x:v>
       </x:c>
       <x:c r="N27" s="7" t="str"/>
       <x:c r="O27" s="7" t="str">
@@ -5209,59 +5271,59 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q27" s="7" t="str">
-        <x:v>RC0201FR-07100RL</x:v>
+        <x:v>R0402</x:v>
       </x:c>
       <x:c r="R27" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C77623.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C60490.html</x:v>
       </x:c>
       <x:c r="S27" s="7" t="str">
-        <x:v>Package: 0201; Power(Watts): 50mW; Resistance: 100Ω; Voltage Rating: 25V; Operating Temperature: -55℃~+125℃; Type: Thick Film Resistor; Tolerance: ±1%; Temperature Coefficient: ±200ppm/℃</x:v>
+        <x:v>Package: 0402; Power(Watts): 62.5mW; Resistance: 10kΩ; Voltage Rating: 50V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±1%</x:v>
       </x:c>
       <x:c r="T27" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls, BOM_PASTER_8984112A_Y189.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R9,R10,R11,R23,R24,R25,R26,R27,R28,R29,R30,R31,R34,R38,R40,R42; BOM_PASTER_8984112A_Y185.xls: R5,R6,R13,R14,R15; BOM_PASTER_8984112A_Y189.xls: R3</x:v>
+        <x:v>Designators: R7, R16, R17, R18, R27, R28, R29, R30, R59, R60, R61, R71, R72, R73, R77, R78, R91, R92, R93, R99</x:v>
       </x:c>
       <x:c r="U27" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V27" s="7" t="str">
-        <x:v>legacy_import</x:v>
+        <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="24" customHeight="1">
       <x:c r="A28" s="7" t="str">
-        <x:v>C82868</x:v>
+        <x:v>C60491</x:v>
       </x:c>
       <x:c r="B28" s="7" t="str">
-        <x:v>RC0402FR-0722KL</x:v>
+        <x:v>RC0402FR-07100KL</x:v>
       </x:c>
       <x:c r="C28" s="7" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D28" s="7" t="str">
-        <x:v>62.5mW 22kΩ 50V Thick Film Resistor ±100ppm/℃ ±1% 0402 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>100kΩ 62.5mW 50V Thick Film Resistor ±100ppm/℃ ±1% 0402 Chip Resistor - Surface Mount RoHS</x:v>
       </x:c>
       <x:c r="E28" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F28" s="7" t="str">
-        <x:v>R_22kohm_0402</x:v>
+        <x:v>R_100kohm_0402</x:v>
       </x:c>
       <x:c r="G28" s="7" t="str">
         <x:v>R_0402_1005Metric</x:v>
       </x:c>
       <x:c r="H28" s="7" t="str">
-        <x:v>22kΩ</x:v>
+        <x:v>100kΩ</x:v>
       </x:c>
       <x:c r="I28" s="7" t="str">
         <x:v>0402</x:v>
       </x:c>
       <x:c r="J28" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C82868</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C60491</x:v>
       </x:c>
       <x:c r="K28" s="7" t="str"/>
       <x:c r="L28" s="7" t="str"/>
       <x:c r="M28" s="7" t="str">
-        <x:v>../datasheets/C82868/RC0402FR-0722KL.pdf</x:v>
+        <x:v>../datasheets/C60491/RC0402FR-07100KL.pdf</x:v>
       </x:c>
       <x:c r="N28" s="7" t="str"/>
       <x:c r="O28" s="7" t="str">
@@ -5271,16 +5333,16 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q28" s="7" t="str">
-        <x:v>RC0402FR-0722KL</x:v>
+        <x:v>RC0402FR-07100KL</x:v>
       </x:c>
       <x:c r="R28" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C82868.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C60491.html</x:v>
       </x:c>
       <x:c r="S28" s="7" t="str">
-        <x:v>Package: 0402; Power(Watts): 62.5mW; Resistance: 22kΩ; Voltage Rating: 50V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±1%</x:v>
+        <x:v>Package: 0402; Resistance: 100kΩ; Power(Watts): 62.5mW; Voltage Rating: 50V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±1%</x:v>
       </x:c>
       <x:c r="T28" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R1,R3,R4</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R14,R19; BOM_PASTER_8984112A_Y185.xls: R19</x:v>
       </x:c>
       <x:c r="U28" s="7" t="str">
         <x:v>METADATA_READY</x:v>
@@ -5291,39 +5353,39 @@
     </x:row>
     <x:row r="29" ht="24" customHeight="1">
       <x:c r="A29" s="7" t="str">
-        <x:v>C851693</x:v>
+        <x:v>C723375</x:v>
       </x:c>
       <x:c r="B29" s="7" t="str">
-        <x:v>RC0201DR-0726K1L</x:v>
+        <x:v>PA2512FKF7T0R003E</x:v>
       </x:c>
       <x:c r="C29" s="7" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D29" s="7" t="str">
-        <x:v>26.1kΩ 50mW 25V Thick Film Resistor ±0.5% ±200ppm/℃ 0201 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>3mΩ ±1% 3W Current Sense Resistor</x:v>
       </x:c>
       <x:c r="E29" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F29" s="7" t="str">
-        <x:v>R_26_1kohm_0201</x:v>
+        <x:v>R_3mohm_2512</x:v>
       </x:c>
       <x:c r="G29" s="7" t="str">
-        <x:v>ExternalDriver_RC0201DR-0726K1L</x:v>
+        <x:v>R_2512_6332Metric</x:v>
       </x:c>
       <x:c r="H29" s="7" t="str">
-        <x:v>26.1kΩ</x:v>
+        <x:v>3mΩ</x:v>
       </x:c>
       <x:c r="I29" s="7" t="str">
-        <x:v>0201</x:v>
+        <x:v>2512</x:v>
       </x:c>
       <x:c r="J29" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C851693</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/5b6b15592a49e0e574b8071c20ab494b.pdf?productCode=C723375</x:v>
       </x:c>
       <x:c r="K29" s="7" t="str"/>
       <x:c r="L29" s="7" t="str"/>
       <x:c r="M29" s="7" t="str">
-        <x:v>../datasheets/C851693/RC0201DR-0726K1L.pdf</x:v>
+        <x:v>../datasheets/C723375/PA2512FKF7T0R003E.pdf</x:v>
       </x:c>
       <x:c r="N29" s="7" t="str"/>
       <x:c r="O29" s="7" t="str">
@@ -5333,59 +5395,59 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q29" s="7" t="str">
-        <x:v>RC0201DR-0726K1L</x:v>
+        <x:v>R2512</x:v>
       </x:c>
       <x:c r="R29" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C851693.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C723375.html</x:v>
       </x:c>
       <x:c r="S29" s="7" t="str">
-        <x:v>Package: 0201; Resistance: 26.1kΩ; Power(Watts): 50mW; Voltage Rating: 25V; Operating Temperature: -55℃~+125℃; Type: Thick Film Resistor; Tolerance: ±0.5%; Temperature Coefficient: ±200ppm/℃</x:v>
+        <x:v>Package: 2512; Power(Watts): 3W; Resistance: 3mΩ; Voltage Rating: -; Type: Current Sense Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±1%</x:v>
       </x:c>
       <x:c r="T29" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R16</x:v>
+        <x:v>Designators: R62, R63, R64</x:v>
       </x:c>
       <x:c r="U29" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V29" s="7" t="str">
-        <x:v>legacy_import</x:v>
+        <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="24" customHeight="1">
       <x:c r="A30" s="7" t="str">
-        <x:v>C93940</x:v>
+        <x:v>C77623</x:v>
       </x:c>
       <x:c r="B30" s="7" t="str">
-        <x:v>RC0402FR-076K8L</x:v>
+        <x:v>RC0201FR-07100RL</x:v>
       </x:c>
       <x:c r="C30" s="7" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D30" s="7" t="str">
-        <x:v>62.5mW 6.8kΩ 50V Thick Film Resistor ±100ppm/℃ ±1% 0402 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>50mW 100Ω 25V Thick Film Resistor ±1% ±200ppm/℃ 0201 Chip Resistor - Surface Mount RoHS</x:v>
       </x:c>
       <x:c r="E30" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F30" s="7" t="str">
-        <x:v>R_6_8kohm_0402</x:v>
+        <x:v>R_100ohm_0201</x:v>
       </x:c>
       <x:c r="G30" s="7" t="str">
-        <x:v>R_0402_1005Metric</x:v>
+        <x:v>ExternalDriver_RC0201FR-07100RL</x:v>
       </x:c>
       <x:c r="H30" s="7" t="str">
-        <x:v>6.8kΩ</x:v>
+        <x:v>100Ω</x:v>
       </x:c>
       <x:c r="I30" s="7" t="str">
-        <x:v>0402</x:v>
+        <x:v>0201</x:v>
       </x:c>
       <x:c r="J30" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C93940</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C77623</x:v>
       </x:c>
       <x:c r="K30" s="7" t="str"/>
       <x:c r="L30" s="7" t="str"/>
       <x:c r="M30" s="7" t="str">
-        <x:v>../datasheets/C93940/RC0402FR-076K8L.pdf</x:v>
+        <x:v>../datasheets/C77623/RC0201FR-07100RL.pdf</x:v>
       </x:c>
       <x:c r="N30" s="7" t="str"/>
       <x:c r="O30" s="7" t="str">
@@ -5395,59 +5457,59 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q30" s="7" t="str">
-        <x:v>R0402</x:v>
+        <x:v>RC0201FR-07100RL</x:v>
       </x:c>
       <x:c r="R30" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C93940.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C77623.html</x:v>
       </x:c>
       <x:c r="S30" s="7" t="str">
-        <x:v>Package: 0402; Power(Watts): 62.5mW; Resistance: 6.8kΩ; Voltage Rating: 50V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±1%</x:v>
+        <x:v>Package: 0201; Power(Watts): 50mW; Resistance: 100Ω; Voltage Rating: 25V; Operating Temperature: -55℃~+125℃; Type: Thick Film Resistor; Tolerance: ±1%; Temperature Coefficient: ±200ppm/℃</x:v>
       </x:c>
       <x:c r="T30" s="7" t="str">
-        <x:v>Designators: R76, R79, R80</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls, BOM_PASTER_8984112A_Y189.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R9,R10,R11,R23,R24,R25,R26,R27,R28,R29,R30,R31,R34,R38,R40,R42; BOM_PASTER_8984112A_Y185.xls: R5,R6,R13,R14,R15; BOM_PASTER_8984112A_Y189.xls: R3</x:v>
       </x:c>
       <x:c r="U30" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V30" s="7" t="str">
-        <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
+        <x:v>legacy_import</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="24" customHeight="1">
       <x:c r="A31" s="7" t="str">
-        <x:v>C93942</x:v>
+        <x:v>C82868</x:v>
       </x:c>
       <x:c r="B31" s="7" t="str">
-        <x:v>RC0402FR-0720KL</x:v>
+        <x:v>RC0402FR-0722KL</x:v>
       </x:c>
       <x:c r="C31" s="7" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D31" s="7" t="str">
-        <x:v>20kΩ 62.5mW 50V Thick Film Resistor ±100ppm/℃ ±1% 0402 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>62.5mW 22kΩ 50V Thick Film Resistor ±100ppm/℃ ±1% 0402 Chip Resistor - Surface Mount RoHS</x:v>
       </x:c>
       <x:c r="E31" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F31" s="7" t="str">
-        <x:v>R_20kohm_0402</x:v>
+        <x:v>R_22kohm_0402</x:v>
       </x:c>
       <x:c r="G31" s="7" t="str">
         <x:v>R_0402_1005Metric</x:v>
       </x:c>
       <x:c r="H31" s="7" t="str">
-        <x:v>20kΩ</x:v>
+        <x:v>22kΩ</x:v>
       </x:c>
       <x:c r="I31" s="7" t="str">
         <x:v>0402</x:v>
       </x:c>
       <x:c r="J31" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C93942</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C82868</x:v>
       </x:c>
       <x:c r="K31" s="7" t="str"/>
       <x:c r="L31" s="7" t="str"/>
       <x:c r="M31" s="7" t="str">
-        <x:v>../datasheets/C93942/RC0402FR-0720KL.pdf</x:v>
+        <x:v>../datasheets/C82868/RC0402FR-0722KL.pdf</x:v>
       </x:c>
       <x:c r="N31" s="7" t="str"/>
       <x:c r="O31" s="7" t="str">
@@ -5457,31 +5519,217 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q31" s="7" t="str">
+        <x:v>RC0402FR-0722KL</x:v>
+      </x:c>
+      <x:c r="R31" s="7" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C82868.html</x:v>
+      </x:c>
+      <x:c r="S31" s="7" t="str">
+        <x:v>Package: 0402; Power(Watts): 62.5mW; Resistance: 22kΩ; Voltage Rating: 50V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±1%</x:v>
+      </x:c>
+      <x:c r="T31" s="7" t="str">
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R1,R3,R4</x:v>
+      </x:c>
+      <x:c r="U31" s="7" t="str">
+        <x:v>METADATA_READY</x:v>
+      </x:c>
+      <x:c r="V31" s="7" t="str">
+        <x:v>X200T_ECU_B1_V1.0_20240809; legacy_import</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="24" customHeight="1">
+      <x:c r="A32" s="7" t="str">
+        <x:v>C851693</x:v>
+      </x:c>
+      <x:c r="B32" s="7" t="str">
+        <x:v>RC0201DR-0726K1L</x:v>
+      </x:c>
+      <x:c r="C32" s="7" t="str">
+        <x:v>YAGEO</x:v>
+      </x:c>
+      <x:c r="D32" s="7" t="str">
+        <x:v>26.1kΩ 50mW 25V Thick Film Resistor ±0.5% ±200ppm/℃ 0201 Chip Resistor - Surface Mount RoHS</x:v>
+      </x:c>
+      <x:c r="E32" s="7" t="str">
+        <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
+      </x:c>
+      <x:c r="F32" s="7" t="str">
+        <x:v>R_26_1kohm_0201</x:v>
+      </x:c>
+      <x:c r="G32" s="7" t="str">
+        <x:v>ExternalDriver_RC0201DR-0726K1L</x:v>
+      </x:c>
+      <x:c r="H32" s="7" t="str">
+        <x:v>26.1kΩ</x:v>
+      </x:c>
+      <x:c r="I32" s="7" t="str">
+        <x:v>0201</x:v>
+      </x:c>
+      <x:c r="J32" s="7" t="str">
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C851693</x:v>
+      </x:c>
+      <x:c r="K32" s="7" t="str"/>
+      <x:c r="L32" s="7" t="str"/>
+      <x:c r="M32" s="7" t="str">
+        <x:v>../datasheets/C851693/RC0201DR-0726K1L.pdf</x:v>
+      </x:c>
+      <x:c r="N32" s="7" t="str"/>
+      <x:c r="O32" s="7" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="P32" s="7" t="str">
+        <x:v>LCSC</x:v>
+      </x:c>
+      <x:c r="Q32" s="7" t="str">
+        <x:v>RC0201DR-0726K1L</x:v>
+      </x:c>
+      <x:c r="R32" s="7" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C851693.html</x:v>
+      </x:c>
+      <x:c r="S32" s="7" t="str">
+        <x:v>Package: 0201; Resistance: 26.1kΩ; Power(Watts): 50mW; Voltage Rating: 25V; Operating Temperature: -55℃~+125℃; Type: Thick Film Resistor; Tolerance: ±0.5%; Temperature Coefficient: ±200ppm/℃</x:v>
+      </x:c>
+      <x:c r="T32" s="7" t="str">
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R16</x:v>
+      </x:c>
+      <x:c r="U32" s="7" t="str">
+        <x:v>METADATA_READY</x:v>
+      </x:c>
+      <x:c r="V32" s="7" t="str">
+        <x:v>legacy_import</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="24" customHeight="1">
+      <x:c r="A33" s="7" t="str">
+        <x:v>C93940</x:v>
+      </x:c>
+      <x:c r="B33" s="7" t="str">
+        <x:v>RC0402FR-076K8L</x:v>
+      </x:c>
+      <x:c r="C33" s="7" t="str">
+        <x:v>YAGEO</x:v>
+      </x:c>
+      <x:c r="D33" s="7" t="str">
+        <x:v>62.5mW 6.8kΩ 50V Thick Film Resistor ±100ppm/℃ ±1% 0402 Chip Resistor - Surface Mount RoHS</x:v>
+      </x:c>
+      <x:c r="E33" s="7" t="str">
+        <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
+      </x:c>
+      <x:c r="F33" s="7" t="str">
+        <x:v>R_6_8kohm_0402</x:v>
+      </x:c>
+      <x:c r="G33" s="7" t="str">
+        <x:v>R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="H33" s="7" t="str">
+        <x:v>6.8kΩ</x:v>
+      </x:c>
+      <x:c r="I33" s="7" t="str">
+        <x:v>0402</x:v>
+      </x:c>
+      <x:c r="J33" s="7" t="str">
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C93940</x:v>
+      </x:c>
+      <x:c r="K33" s="7" t="str"/>
+      <x:c r="L33" s="7" t="str"/>
+      <x:c r="M33" s="7" t="str">
+        <x:v>../datasheets/C93940/RC0402FR-076K8L.pdf</x:v>
+      </x:c>
+      <x:c r="N33" s="7" t="str"/>
+      <x:c r="O33" s="7" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="P33" s="7" t="str">
+        <x:v>LCSC</x:v>
+      </x:c>
+      <x:c r="Q33" s="7" t="str">
         <x:v>R0402</x:v>
       </x:c>
-      <x:c r="R31" s="7" t="str">
+      <x:c r="R33" s="7" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C93940.html</x:v>
+      </x:c>
+      <x:c r="S33" s="7" t="str">
+        <x:v>Package: 0402; Power(Watts): 62.5mW; Resistance: 6.8kΩ; Voltage Rating: 50V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±1%</x:v>
+      </x:c>
+      <x:c r="T33" s="7" t="str">
+        <x:v>Designators: R76, R79, R80</x:v>
+      </x:c>
+      <x:c r="U33" s="7" t="str">
+        <x:v>METADATA_READY</x:v>
+      </x:c>
+      <x:c r="V33" s="7" t="str">
+        <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="24" customHeight="1">
+      <x:c r="A34" s="7" t="str">
+        <x:v>C93942</x:v>
+      </x:c>
+      <x:c r="B34" s="7" t="str">
+        <x:v>RC0402FR-0720KL</x:v>
+      </x:c>
+      <x:c r="C34" s="7" t="str">
+        <x:v>YAGEO</x:v>
+      </x:c>
+      <x:c r="D34" s="7" t="str">
+        <x:v>20kΩ 62.5mW 50V Thick Film Resistor ±100ppm/℃ ±1% 0402 Chip Resistor - Surface Mount RoHS</x:v>
+      </x:c>
+      <x:c r="E34" s="7" t="str">
+        <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
+      </x:c>
+      <x:c r="F34" s="7" t="str">
+        <x:v>R_20kohm_0402</x:v>
+      </x:c>
+      <x:c r="G34" s="7" t="str">
+        <x:v>R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="H34" s="7" t="str">
+        <x:v>20kΩ</x:v>
+      </x:c>
+      <x:c r="I34" s="7" t="str">
+        <x:v>0402</x:v>
+      </x:c>
+      <x:c r="J34" s="7" t="str">
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C93942</x:v>
+      </x:c>
+      <x:c r="K34" s="7" t="str"/>
+      <x:c r="L34" s="7" t="str"/>
+      <x:c r="M34" s="7" t="str">
+        <x:v>../datasheets/C93942/RC0402FR-0720KL.pdf</x:v>
+      </x:c>
+      <x:c r="N34" s="7" t="str"/>
+      <x:c r="O34" s="7" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="P34" s="7" t="str">
+        <x:v>LCSC</x:v>
+      </x:c>
+      <x:c r="Q34" s="7" t="str">
+        <x:v>R0402</x:v>
+      </x:c>
+      <x:c r="R34" s="7" t="str">
         <x:v>https://www.lcsc.com/product-detail/C93942.html</x:v>
       </x:c>
-      <x:c r="S31" s="7" t="str">
+      <x:c r="S34" s="7" t="str">
         <x:v>Package: 0402; Resistance: 20kΩ; Power(Watts): 62.5mW; Voltage Rating: 50V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±1%</x:v>
       </x:c>
-      <x:c r="T31" s="7" t="str">
+      <x:c r="T34" s="7" t="str">
         <x:v>Designators: R75</x:v>
       </x:c>
-      <x:c r="U31" s="7" t="str">
-        <x:v>METADATA_READY</x:v>
-      </x:c>
-      <x:c r="V31" s="7" t="str">
+      <x:c r="U34" s="7" t="str">
+        <x:v>METADATA_READY</x:v>
+      </x:c>
+      <x:c r="V34" s="7" t="str">
         <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="U5:U31">
+  <x:conditionalFormatting sqref="U5:U34">
     <x:cfRule type="containsText" dxfId="15" priority="1" operator="containsText" text="CLASSIFIED_PARTIAL"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R589a72e2a0b745e8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53356df01bac43a7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5660,7 +5908,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf977bfa4260844ad"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R696bb19aec724000"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5839,7 +6087,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74ed8ef64d2c4aab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7f8d6bec08247d2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5879,7 +6127,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="2" t="str">
-        <x:v>类别：Capacitors；记录数：27；来源：all_parts.csv</x:v>
+        <x:v>类别：Capacitors；记录数：31；来源：all_parts.csv</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -6510,39 +6758,39 @@
     </x:row>
     <x:row r="14" ht="24" customHeight="1">
       <x:c r="A14" s="7" t="str">
-        <x:v>C3039698</x:v>
+        <x:v>C29936</x:v>
       </x:c>
       <x:c r="B14" s="7" t="str">
-        <x:v>CL10B106MQ8NRNC</x:v>
+        <x:v>CL10B105KA8NNNC</x:v>
       </x:c>
       <x:c r="C14" s="7" t="str">
-        <x:v>Samsung Electro-Mechanics</x:v>
+        <x:v>SAMSUNG(三星)</x:v>
       </x:c>
       <x:c r="D14" s="7" t="str">
-        <x:v>10uF ±20% 6.3V Ceramic Capacitor X7R 0603</x:v>
+        <x:v>1uF 25V X7R 0603 ceramic capacitor</x:v>
       </x:c>
       <x:c r="E14" s="7" t="str">
         <x:v>Capacitors/Ceramic Capacitors</x:v>
       </x:c>
       <x:c r="F14" s="7" t="str">
-        <x:v>C_10uF_0603</x:v>
+        <x:v>C_1uF_0603</x:v>
       </x:c>
       <x:c r="G14" s="7" t="str">
         <x:v>C_0603_1608Metric</x:v>
       </x:c>
       <x:c r="H14" s="7" t="str">
-        <x:v>10uF</x:v>
+        <x:v>1uF</x:v>
       </x:c>
       <x:c r="I14" s="7" t="str">
         <x:v>0603</x:v>
       </x:c>
       <x:c r="J14" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/25aeaed41ae8f3c7d2a7fa32796a6299.pdf?productCode=C3039698</x:v>
+        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20160218/1457707763339.pdf</x:v>
       </x:c>
       <x:c r="K14" s="7" t="str"/>
       <x:c r="L14" s="7" t="str"/>
       <x:c r="M14" s="7" t="str">
-        <x:v>../datasheets/C3039698/CL10B106MQ8NRNC.pdf</x:v>
+        <x:v>../datasheets/C29936/CL10B105KA8NNNC.pdf</x:v>
       </x:c>
       <x:c r="N14" s="7" t="str"/>
       <x:c r="O14" s="7" t="str">
@@ -6552,55 +6800,59 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str">
-        <x:v>0603-10uF-6.3V-20%</x:v>
+        <x:v>C0603</x:v>
       </x:c>
       <x:c r="R14" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C3039698.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C29936.html</x:v>
       </x:c>
       <x:c r="S14" s="7" t="str">
-        <x:v>Package: 0603; Capacitance: 10uF; Temperature Coefficient: X7R; Tolerance: ±20%; Voltage Rating: 6.3V</x:v>
+        <x:v>Package: 0603; Capacitance: 1uF; Voltage: 25V; Tolerance: 10%; Temperature Coefficient: X7R</x:v>
       </x:c>
       <x:c r="T14" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: C20</x:v>
+        <x:v>EBOM BOM_QS01_GD32F503_V1.10; designators C11/C13/C21.</x:v>
       </x:c>
       <x:c r="U14" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V14" s="7" t="str">
-        <x:v>legacy_import</x:v>
+        <x:v>EBOM_V1.10</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
       <x:c r="A15" s="7" t="str">
-        <x:v>C307331</x:v>
+        <x:v>C3039698</x:v>
       </x:c>
       <x:c r="B15" s="7" t="str">
-        <x:v>CL05B104KB54PNC</x:v>
+        <x:v>CL10B106MQ8NRNC</x:v>
       </x:c>
       <x:c r="C15" s="7" t="str">
-        <x:v>SAMSUNG</x:v>
+        <x:v>Samsung Electro-Mechanics</x:v>
       </x:c>
       <x:c r="D15" s="7" t="str">
-        <x:v>100nF ±10% 50V Ceramic Capacitor X7R</x:v>
+        <x:v>10uF ±20% 6.3V Ceramic Capacitor X7R 0603</x:v>
       </x:c>
       <x:c r="E15" s="7" t="str">
         <x:v>Capacitors/Ceramic Capacitors</x:v>
       </x:c>
-      <x:c r="F15" s="7" t="str"/>
-      <x:c r="G15" s="7" t="str"/>
+      <x:c r="F15" s="7" t="str">
+        <x:v>C_10uF_0603</x:v>
+      </x:c>
+      <x:c r="G15" s="7" t="str">
+        <x:v>C_0603_1608Metric</x:v>
+      </x:c>
       <x:c r="H15" s="7" t="str">
-        <x:v>100nF</x:v>
+        <x:v>10uF</x:v>
       </x:c>
       <x:c r="I15" s="7" t="str">
-        <x:v>0402</x:v>
+        <x:v>0603</x:v>
       </x:c>
       <x:c r="J15" s="7" t="str">
-        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20160218/1457707763339.pdf</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/25aeaed41ae8f3c7d2a7fa32796a6299.pdf?productCode=C3039698</x:v>
       </x:c>
       <x:c r="K15" s="7" t="str"/>
       <x:c r="L15" s="7" t="str"/>
       <x:c r="M15" s="7" t="str">
-        <x:v>../datasheets/C307331/CL05B104KB54PNC.pdf</x:v>
+        <x:v>../datasheets/C3039698/CL10B106MQ8NRNC.pdf</x:v>
       </x:c>
       <x:c r="N15" s="7" t="str"/>
       <x:c r="O15" s="7" t="str">
@@ -6610,59 +6862,55 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q15" s="7" t="str">
-        <x:v>0402-100nF-50V-10%</x:v>
+        <x:v>0603-10uF-6.3V-20%</x:v>
       </x:c>
       <x:c r="R15" s="7" t="str">
-        <x:v>https://item.szlcsc.com/291005.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C3039698.html</x:v>
       </x:c>
       <x:c r="S15" s="7" t="str">
-        <x:v>Package: 0402; Capacitance: 100nF; Tolerance: ±10%; Voltage Rating: 50V; Temperature Coefficient: X7R</x:v>
+        <x:v>Package: 0603; Capacitance: 10uF; Temperature Coefficient: X7R; Tolerance: ±20%; Voltage Rating: 6.3V</x:v>
       </x:c>
       <x:c r="T15" s="7" t="str">
-        <x:v>Designators: Y43-C1,C3,C6,C9,C10,C12,C14,C15,C18</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: C20</x:v>
       </x:c>
       <x:c r="U15" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V15" s="7" t="str">
-        <x:v>Y43</x:v>
+        <x:v>legacy_import</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="24" customHeight="1">
       <x:c r="A16" s="7" t="str">
-        <x:v>C329936</x:v>
+        <x:v>C307331</x:v>
       </x:c>
       <x:c r="B16" s="7" t="str">
-        <x:v>CGA4J1X7S1C106KT000N</x:v>
+        <x:v>CL05B104KB54PNC</x:v>
       </x:c>
       <x:c r="C16" s="7" t="str">
-        <x:v>TDK</x:v>
+        <x:v>SAMSUNG</x:v>
       </x:c>
       <x:c r="D16" s="7" t="str">
-        <x:v>10uF ±10% 16V Ceramic Capacitor X7S 0805</x:v>
+        <x:v>100nF ±10% 50V Ceramic Capacitor X7R</x:v>
       </x:c>
       <x:c r="E16" s="7" t="str">
         <x:v>Capacitors/Ceramic Capacitors</x:v>
       </x:c>
-      <x:c r="F16" s="7" t="str">
-        <x:v>C_10uF_0805</x:v>
-      </x:c>
-      <x:c r="G16" s="7" t="str">
-        <x:v>C_0805_2012Metric</x:v>
-      </x:c>
+      <x:c r="F16" s="7" t="str"/>
+      <x:c r="G16" s="7" t="str"/>
       <x:c r="H16" s="7" t="str">
-        <x:v>10uF</x:v>
+        <x:v>100nF</x:v>
       </x:c>
       <x:c r="I16" s="7" t="str">
-        <x:v>0805</x:v>
+        <x:v>0402</x:v>
       </x:c>
       <x:c r="J16" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/fb3179df2df2fa358ee13dff52d60ee7.pdf?productCode=C329936</x:v>
+        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20160218/1457707763339.pdf</x:v>
       </x:c>
       <x:c r="K16" s="7" t="str"/>
       <x:c r="L16" s="7" t="str"/>
       <x:c r="M16" s="7" t="str">
-        <x:v>../datasheets/C329936/CGA4J1X7S1C106KT000N.pdf</x:v>
+        <x:v>../datasheets/C307331/CL05B104KB54PNC.pdf</x:v>
       </x:c>
       <x:c r="N16" s="7" t="str"/>
       <x:c r="O16" s="7" t="str">
@@ -6672,140 +6920,140 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q16" s="7" t="str">
-        <x:v>C0805</x:v>
+        <x:v>0402-100nF-50V-10%</x:v>
       </x:c>
       <x:c r="R16" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C329936.html</x:v>
+        <x:v>https://item.szlcsc.com/291005.html</x:v>
       </x:c>
       <x:c r="S16" s="7" t="str">
-        <x:v>Package: 0805; Capacitance: 10uF; Temperature Coefficient: X7S; Tolerance: ±10%; Voltage Rating: 16V</x:v>
+        <x:v>Package: 0402; Capacitance: 100nF; Tolerance: ±10%; Voltage Rating: 50V; Temperature Coefficient: X7R</x:v>
       </x:c>
       <x:c r="T16" s="7" t="str">
-        <x:v>Designators: C9, C11, C16, C21, C22, C79, C80</x:v>
+        <x:v>Designators: Y43-C1,C3,C6,C9,C10,C12,C14,C15,C18</x:v>
       </x:c>
       <x:c r="U16" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V16" s="7" t="str">
-        <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
+        <x:v>Y43</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="24" customHeight="1">
       <x:c r="A17" s="7" t="str">
-        <x:v>C382253</x:v>
+        <x:v>C329936</x:v>
       </x:c>
       <x:c r="B17" s="7" t="str">
-        <x:v>FM18X222K101PSG</x:v>
+        <x:v>CGA4J1X7S1C106KT000N</x:v>
       </x:c>
       <x:c r="C17" s="7" t="str">
-        <x:v>PSA</x:v>
+        <x:v>TDK</x:v>
       </x:c>
       <x:c r="D17" s="7" t="str">
-        <x:v>2.2nF ±10% 100V Ceramic Capacitor X7R 0603</x:v>
+        <x:v>10uF ±10% 16V Ceramic Capacitor X7S 0805</x:v>
       </x:c>
       <x:c r="E17" s="7" t="str">
         <x:v>Capacitors/Ceramic Capacitors</x:v>
       </x:c>
       <x:c r="F17" s="7" t="str">
-        <x:v>C_2_2nF_0603</x:v>
+        <x:v>C_10uF_0805</x:v>
       </x:c>
       <x:c r="G17" s="7" t="str">
-        <x:v>C_0603_1608Metric</x:v>
+        <x:v>C_0805_2012Metric</x:v>
       </x:c>
       <x:c r="H17" s="7" t="str">
-        <x:v>2.2nF</x:v>
+        <x:v>10uF</x:v>
       </x:c>
       <x:c r="I17" s="7" t="str">
-        <x:v>0603</x:v>
+        <x:v>0805</x:v>
       </x:c>
       <x:c r="J17" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/8aced6bf19551db75d1c722c291966af.pdf?productCode=C382253</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/fb3179df2df2fa358ee13dff52d60ee7.pdf?productCode=C329936</x:v>
       </x:c>
       <x:c r="K17" s="7" t="str"/>
       <x:c r="L17" s="7" t="str"/>
       <x:c r="M17" s="7" t="str">
-        <x:v>../datasheets/C382253/FM18X222K101PSG.pdf</x:v>
+        <x:v>../datasheets/C329936/CGA4J1X7S1C106KT000N.pdf</x:v>
       </x:c>
       <x:c r="N17" s="7" t="str"/>
       <x:c r="O17" s="7" t="str">
-        <x:v>OutOfStock</x:v>
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="P17" s="7" t="str">
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q17" s="7" t="str">
-        <x:v>0603-2.2nF-100V-10%</x:v>
+        <x:v>C0805</x:v>
       </x:c>
       <x:c r="R17" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C382253.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C329936.html</x:v>
       </x:c>
       <x:c r="S17" s="7" t="str">
-        <x:v>Package: 0603; Capacitance: 2.2nF; Temperature Coefficient: X7R; Tolerance: ±10%; Voltage Rating: 100V</x:v>
+        <x:v>Package: 0805; Capacitance: 10uF; Temperature Coefficient: X7S; Tolerance: ±10%; Voltage Rating: 16V</x:v>
       </x:c>
       <x:c r="T17" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: C61,C62,C63</x:v>
+        <x:v>Designators: C9, C11, C16, C21, C22, C79, C80</x:v>
       </x:c>
       <x:c r="U17" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V17" s="7" t="str">
-        <x:v>legacy_import</x:v>
+        <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="24" customHeight="1">
       <x:c r="A18" s="7" t="str">
-        <x:v>C5156756</x:v>
+        <x:v>C382253</x:v>
       </x:c>
       <x:c r="B18" s="7" t="str">
-        <x:v>FS32X106K101EGG</x:v>
+        <x:v>FM18X222K101PSG</x:v>
       </x:c>
       <x:c r="C18" s="7" t="str">
         <x:v>PSA</x:v>
       </x:c>
       <x:c r="D18" s="7" t="str">
-        <x:v>10uF ±10% 100V Ceramic Capacitor X7R 1210</x:v>
+        <x:v>2.2nF ±10% 100V Ceramic Capacitor X7R 0603</x:v>
       </x:c>
       <x:c r="E18" s="7" t="str">
         <x:v>Capacitors/Ceramic Capacitors</x:v>
       </x:c>
       <x:c r="F18" s="7" t="str">
-        <x:v>C_10uF_1210</x:v>
+        <x:v>C_2_2nF_0603</x:v>
       </x:c>
       <x:c r="G18" s="7" t="str">
-        <x:v>C_1210_3225Metric</x:v>
+        <x:v>C_0603_1608Metric</x:v>
       </x:c>
       <x:c r="H18" s="7" t="str">
-        <x:v>10uF</x:v>
+        <x:v>2.2nF</x:v>
       </x:c>
       <x:c r="I18" s="7" t="str">
-        <x:v>1210</x:v>
+        <x:v>0603</x:v>
       </x:c>
       <x:c r="J18" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/18a0c9f8bf4d73d021cc722eccd020e0.pdf?productCode=C5156756</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/8aced6bf19551db75d1c722c291966af.pdf?productCode=C382253</x:v>
       </x:c>
       <x:c r="K18" s="7" t="str"/>
       <x:c r="L18" s="7" t="str"/>
       <x:c r="M18" s="7" t="str">
-        <x:v>../datasheets/C5156756/FS32X106K101EGG.pdf</x:v>
+        <x:v>../datasheets/C382253/FM18X222K101PSG.pdf</x:v>
       </x:c>
       <x:c r="N18" s="7" t="str"/>
       <x:c r="O18" s="7" t="str">
-        <x:v>Active</x:v>
+        <x:v>OutOfStock</x:v>
       </x:c>
       <x:c r="P18" s="7" t="str">
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q18" s="7" t="str">
-        <x:v>1210-10uF-100V-10%</x:v>
+        <x:v>0603-2.2nF-100V-10%</x:v>
       </x:c>
       <x:c r="R18" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C5156756.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C382253.html</x:v>
       </x:c>
       <x:c r="S18" s="7" t="str">
-        <x:v>Package: 1210; Capacitance: 10uF; Temperature Coefficient: X7R; Tolerance: ±10%; Voltage Rating: 100V</x:v>
+        <x:v>Package: 0603; Capacitance: 2.2nF; Temperature Coefficient: X7R; Tolerance: ±10%; Voltage Rating: 100V</x:v>
       </x:c>
       <x:c r="T18" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: C8,C16,C17,C22</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: C61,C62,C63</x:v>
       </x:c>
       <x:c r="U18" s="7" t="str">
         <x:v>METADATA_READY</x:v>
@@ -6816,39 +7064,39 @@
     </x:row>
     <x:row r="19" ht="24" customHeight="1">
       <x:c r="A19" s="7" t="str">
-        <x:v>C525226</x:v>
+        <x:v>C445740</x:v>
       </x:c>
       <x:c r="B19" s="7" t="str">
-        <x:v>FN15X104K500PKG</x:v>
+        <x:v>C1005X7S1A225KT000E</x:v>
       </x:c>
       <x:c r="C19" s="7" t="str">
-        <x:v>PSA</x:v>
+        <x:v>TDK</x:v>
       </x:c>
       <x:c r="D19" s="7" t="str">
-        <x:v>100nF ±10% 50V Ceramic Capacitor X7R 0402</x:v>
+        <x:v>2.2uF 10V X7S 0402 ceramic capacitor</x:v>
       </x:c>
       <x:c r="E19" s="7" t="str">
         <x:v>Capacitors/Ceramic Capacitors</x:v>
       </x:c>
       <x:c r="F19" s="7" t="str">
-        <x:v>C_100nF_0402</x:v>
+        <x:v>C_2_2uF_0402</x:v>
       </x:c>
       <x:c r="G19" s="7" t="str">
         <x:v>C_0402_1005Metric</x:v>
       </x:c>
       <x:c r="H19" s="7" t="str">
-        <x:v>100nF</x:v>
+        <x:v>2.2uF</x:v>
       </x:c>
       <x:c r="I19" s="7" t="str">
         <x:v>0402</x:v>
       </x:c>
       <x:c r="J19" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/3d771c0c586676719f80e96a0f8d9dcd.pdf?productCode=C525226</x:v>
+        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20191108/C445765_930F403C9F9F1C91FA65B6959DB97EFA.pdf</x:v>
       </x:c>
       <x:c r="K19" s="7" t="str"/>
       <x:c r="L19" s="7" t="str"/>
       <x:c r="M19" s="7" t="str">
-        <x:v>../datasheets/C525226/FN15X104K500PKG.pdf</x:v>
+        <x:v>../datasheets/C445740/C1005X7S1A225KT000E.pdf</x:v>
       </x:c>
       <x:c r="N19" s="7" t="str"/>
       <x:c r="O19" s="7" t="str">
@@ -6858,59 +7106,59 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q19" s="7" t="str">
-        <x:v>0402-100nF-50V-10%</x:v>
+        <x:v>C0402</x:v>
       </x:c>
       <x:c r="R19" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C525226.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C445740.html</x:v>
       </x:c>
       <x:c r="S19" s="7" t="str">
-        <x:v>Package: 0402; Capacitance: 100nF; Temperature Coefficient: X7R; Tolerance: ±10%; Voltage Rating: 50V</x:v>
+        <x:v>Package: 0402; Capacitance: 2.2uF; Voltage: 10V; Tolerance: 10%; Temperature Coefficient: X7S</x:v>
       </x:c>
       <x:c r="T19" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y182.xls: C19; BOM_PASTER_8984112A_Y185.xls: C5</x:v>
+        <x:v>EBOM BOM_QS01_GD32F503_V1.10; designator C19.</x:v>
       </x:c>
       <x:c r="U19" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V19" s="7" t="str">
-        <x:v>legacy_import</x:v>
+        <x:v>EBOM_V1.10</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="24" customHeight="1">
       <x:c r="A20" s="7" t="str">
-        <x:v>C527014</x:v>
+        <x:v>C5156756</x:v>
       </x:c>
       <x:c r="B20" s="7" t="str">
-        <x:v>CC0402KRX7R0BB103</x:v>
+        <x:v>FS32X106K101EGG</x:v>
       </x:c>
       <x:c r="C20" s="7" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>PSA</x:v>
       </x:c>
       <x:c r="D20" s="7" t="str">
-        <x:v>10nF ±10% 100V Ceramic Capacitor X7R 0402</x:v>
+        <x:v>10uF ±10% 100V Ceramic Capacitor X7R 1210</x:v>
       </x:c>
       <x:c r="E20" s="7" t="str">
         <x:v>Capacitors/Ceramic Capacitors</x:v>
       </x:c>
       <x:c r="F20" s="7" t="str">
-        <x:v>C_10nF_0402</x:v>
+        <x:v>C_10uF_1210</x:v>
       </x:c>
       <x:c r="G20" s="7" t="str">
-        <x:v>C_0402_1005Metric</x:v>
+        <x:v>C_1210_3225Metric</x:v>
       </x:c>
       <x:c r="H20" s="7" t="str">
-        <x:v>10nF</x:v>
+        <x:v>10uF</x:v>
       </x:c>
       <x:c r="I20" s="7" t="str">
-        <x:v>0402</x:v>
+        <x:v>1210</x:v>
       </x:c>
       <x:c r="J20" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/23ccee80ee542e7cf156a772bb589942.pdf?productCode=C527014</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/18a0c9f8bf4d73d021cc722eccd020e0.pdf?productCode=C5156756</x:v>
       </x:c>
       <x:c r="K20" s="7" t="str"/>
       <x:c r="L20" s="7" t="str"/>
       <x:c r="M20" s="7" t="str">
-        <x:v>../datasheets/C527014/CC0402KRX7R0BB103.pdf</x:v>
+        <x:v>../datasheets/C5156756/FS32X106K101EGG.pdf</x:v>
       </x:c>
       <x:c r="N20" s="7" t="str"/>
       <x:c r="O20" s="7" t="str">
@@ -6920,16 +7168,16 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q20" s="7" t="str">
-        <x:v>CC0402KRX7R0BB103</x:v>
+        <x:v>1210-10uF-100V-10%</x:v>
       </x:c>
       <x:c r="R20" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C527014.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C5156756.html</x:v>
       </x:c>
       <x:c r="S20" s="7" t="str">
-        <x:v>Package: 0402; Capacitance: 10nF; Temperature Coefficient: X7R; Tolerance: ±10%; Voltage Rating: 100V</x:v>
+        <x:v>Package: 1210; Capacitance: 10uF; Temperature Coefficient: X7R; Tolerance: ±10%; Voltage Rating: 100V</x:v>
       </x:c>
       <x:c r="T20" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: C52</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: C8,C16,C17,C22</x:v>
       </x:c>
       <x:c r="U20" s="7" t="str">
         <x:v>METADATA_READY</x:v>
@@ -6940,35 +7188,39 @@
     </x:row>
     <x:row r="21" ht="24" customHeight="1">
       <x:c r="A21" s="7" t="str">
-        <x:v>C52923</x:v>
+        <x:v>C525226</x:v>
       </x:c>
       <x:c r="B21" s="7" t="str">
-        <x:v>CL05A105KA5NQNC</x:v>
+        <x:v>FN15X104K500PKG</x:v>
       </x:c>
       <x:c r="C21" s="7" t="str">
-        <x:v>SAMSUNG</x:v>
+        <x:v>PSA</x:v>
       </x:c>
       <x:c r="D21" s="7" t="str">
-        <x:v>1uF ±10% 25V Ceramic Capacitor X5R</x:v>
+        <x:v>100nF ±10% 50V Ceramic Capacitor X7R 0402</x:v>
       </x:c>
       <x:c r="E21" s="7" t="str">
         <x:v>Capacitors/Ceramic Capacitors</x:v>
       </x:c>
-      <x:c r="F21" s="7" t="str"/>
-      <x:c r="G21" s="7" t="str"/>
+      <x:c r="F21" s="7" t="str">
+        <x:v>C_100nF_0402</x:v>
+      </x:c>
+      <x:c r="G21" s="7" t="str">
+        <x:v>C_0402_1005Metric</x:v>
+      </x:c>
       <x:c r="H21" s="7" t="str">
-        <x:v>1uF</x:v>
+        <x:v>100nF</x:v>
       </x:c>
       <x:c r="I21" s="7" t="str">
         <x:v>0402</x:v>
       </x:c>
       <x:c r="J21" s="7" t="str">
-        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20160218/1457707763339.pdf</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/3d771c0c586676719f80e96a0f8d9dcd.pdf?productCode=C525226</x:v>
       </x:c>
       <x:c r="K21" s="7" t="str"/>
       <x:c r="L21" s="7" t="str"/>
       <x:c r="M21" s="7" t="str">
-        <x:v>../datasheets/C52923/CL05A105KA5NQNC.pdf</x:v>
+        <x:v>../datasheets/C525226/FN15X104K500PKG.pdf</x:v>
       </x:c>
       <x:c r="N21" s="7" t="str"/>
       <x:c r="O21" s="7" t="str">
@@ -6978,78 +7230,78 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q21" s="7" t="str">
-        <x:v>0402-1uF-10V-10%</x:v>
+        <x:v>0402-100nF-50V-10%</x:v>
       </x:c>
       <x:c r="R21" s="7" t="str">
-        <x:v>https://item.szlcsc.com/53938.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C525226.html</x:v>
       </x:c>
       <x:c r="S21" s="7" t="str">
-        <x:v>Package: 0402; Capacitance: 1uF; Tolerance: ±10%; Voltage Rating: 25V; Temperature Coefficient: X5R</x:v>
+        <x:v>Package: 0402; Capacitance: 100nF; Temperature Coefficient: X7R; Tolerance: ±10%; Voltage Rating: 50V</x:v>
       </x:c>
       <x:c r="T21" s="7" t="str">
-        <x:v>Designators: Y43-C2,C4,C5,C7,C16</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y182.xls: C19; BOM_PASTER_8984112A_Y185.xls: C5</x:v>
       </x:c>
       <x:c r="U21" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V21" s="7" t="str">
-        <x:v>Y43</x:v>
+        <x:v>legacy_import</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="24" customHeight="1">
       <x:c r="A22" s="7" t="str">
-        <x:v>C561710</x:v>
+        <x:v>C527014</x:v>
       </x:c>
       <x:c r="B22" s="7" t="str">
-        <x:v>FN03N100J500PLG</x:v>
+        <x:v>CC0402KRX7R0BB103</x:v>
       </x:c>
       <x:c r="C22" s="7" t="str">
-        <x:v>PSA</x:v>
+        <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D22" s="7" t="str">
-        <x:v>10pF ±5% 50V Ceramic Capacitor C0G 0201</x:v>
+        <x:v>10nF ±10% 100V Ceramic Capacitor X7R 0402</x:v>
       </x:c>
       <x:c r="E22" s="7" t="str">
         <x:v>Capacitors/Ceramic Capacitors</x:v>
       </x:c>
       <x:c r="F22" s="7" t="str">
-        <x:v>C_10pF_0201</x:v>
+        <x:v>C_10nF_0402</x:v>
       </x:c>
       <x:c r="G22" s="7" t="str">
-        <x:v>ExternalDriver_0201-10pF-50V-10</x:v>
+        <x:v>C_0402_1005Metric</x:v>
       </x:c>
       <x:c r="H22" s="7" t="str">
-        <x:v>10pF</x:v>
+        <x:v>10nF</x:v>
       </x:c>
       <x:c r="I22" s="7" t="str">
-        <x:v>0201</x:v>
+        <x:v>0402</x:v>
       </x:c>
       <x:c r="J22" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/1497a6a2cea2f2b0acf5e045d2bc193c.pdf?productCode=C561710</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/23ccee80ee542e7cf156a772bb589942.pdf?productCode=C527014</x:v>
       </x:c>
       <x:c r="K22" s="7" t="str"/>
       <x:c r="L22" s="7" t="str"/>
       <x:c r="M22" s="7" t="str">
-        <x:v>../datasheets/C561710/FN03N100J500PLG.pdf</x:v>
+        <x:v>../datasheets/C527014/CC0402KRX7R0BB103.pdf</x:v>
       </x:c>
       <x:c r="N22" s="7" t="str"/>
       <x:c r="O22" s="7" t="str">
-        <x:v>OutOfStock</x:v>
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="P22" s="7" t="str">
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q22" s="7" t="str">
-        <x:v>0201-10pF-50V-10%</x:v>
+        <x:v>CC0402KRX7R0BB103</x:v>
       </x:c>
       <x:c r="R22" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C561710.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C527014.html</x:v>
       </x:c>
       <x:c r="S22" s="7" t="str">
-        <x:v>Package: 0201; Capacitance: 10pF; Temperature Coefficient: C0G; Tolerance: ±5%; Voltage Rating: 50V</x:v>
+        <x:v>Package: 0402; Capacitance: 10nF; Temperature Coefficient: X7R; Tolerance: ±10%; Voltage Rating: 100V</x:v>
       </x:c>
       <x:c r="T22" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: C29,C32</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: C52</x:v>
       </x:c>
       <x:c r="U22" s="7" t="str">
         <x:v>METADATA_READY</x:v>
@@ -7060,39 +7312,35 @@
     </x:row>
     <x:row r="23" ht="24" customHeight="1">
       <x:c r="A23" s="7" t="str">
-        <x:v>C576517</x:v>
+        <x:v>C52923</x:v>
       </x:c>
       <x:c r="B23" s="7" t="str">
-        <x:v>GRM32EC72A106KE05L</x:v>
+        <x:v>CL05A105KA5NQNC</x:v>
       </x:c>
       <x:c r="C23" s="7" t="str">
-        <x:v>muRata</x:v>
+        <x:v>SAMSUNG</x:v>
       </x:c>
       <x:c r="D23" s="7" t="str">
-        <x:v>10uF ±10% 100V Ceramic Capacitor X7S 1210</x:v>
+        <x:v>1uF ±10% 25V Ceramic Capacitor X5R</x:v>
       </x:c>
       <x:c r="E23" s="7" t="str">
         <x:v>Capacitors/Ceramic Capacitors</x:v>
       </x:c>
-      <x:c r="F23" s="7" t="str">
-        <x:v>C_10uF_1210</x:v>
-      </x:c>
-      <x:c r="G23" s="7" t="str">
-        <x:v>C_1210_3225Metric</x:v>
-      </x:c>
+      <x:c r="F23" s="7" t="str"/>
+      <x:c r="G23" s="7" t="str"/>
       <x:c r="H23" s="7" t="str">
-        <x:v>10uF</x:v>
+        <x:v>1uF</x:v>
       </x:c>
       <x:c r="I23" s="7" t="str">
-        <x:v>1210</x:v>
+        <x:v>0402</x:v>
       </x:c>
       <x:c r="J23" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/a5661d5fbdf2b41a50853cb83d84d655.pdf?productCode=C576517</x:v>
+        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20160218/1457707763339.pdf</x:v>
       </x:c>
       <x:c r="K23" s="7" t="str"/>
       <x:c r="L23" s="7" t="str"/>
       <x:c r="M23" s="7" t="str">
-        <x:v>../datasheets/C576517/GRM32EC72A106KE05L.pdf</x:v>
+        <x:v>../datasheets/C52923/CL05A105KA5NQNC.pdf</x:v>
       </x:c>
       <x:c r="N23" s="7" t="str"/>
       <x:c r="O23" s="7" t="str">
@@ -7102,121 +7350,121 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q23" s="7" t="str">
-        <x:v>C1210</x:v>
+        <x:v>0402-1uF-10V-10%</x:v>
       </x:c>
       <x:c r="R23" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C576517.html</x:v>
+        <x:v>https://item.szlcsc.com/53938.html</x:v>
       </x:c>
       <x:c r="S23" s="7" t="str">
-        <x:v>Package: 1210; Capacitance: 10uF; Temperature Coefficient: X7S; Tolerance: ±10%; Voltage Rating: 100V</x:v>
+        <x:v>Package: 0402; Capacitance: 1uF; Tolerance: ±10%; Voltage Rating: 25V; Temperature Coefficient: X5R</x:v>
       </x:c>
       <x:c r="T23" s="7" t="str">
-        <x:v>Designators: C2, C3, C5, C6, C7, C8, C17, C46, C47, C48, C81, C82, C83, C87, C88</x:v>
+        <x:v>Designators: Y43-C2,C4,C5,C7,C16</x:v>
       </x:c>
       <x:c r="U23" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V23" s="7" t="str">
-        <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
+        <x:v>Y43</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="24" customHeight="1">
       <x:c r="A24" s="7" t="str">
-        <x:v>C577211</x:v>
+        <x:v>C561710</x:v>
       </x:c>
       <x:c r="B24" s="7" t="str">
-        <x:v>CC1206KKX7R0BB225</x:v>
+        <x:v>FN03N100J500PLG</x:v>
       </x:c>
       <x:c r="C24" s="7" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>PSA</x:v>
       </x:c>
       <x:c r="D24" s="7" t="str">
-        <x:v>2.2uF ±10% 100V Ceramic Capacitor X7R 1206</x:v>
+        <x:v>10pF ±5% 50V Ceramic Capacitor C0G 0201</x:v>
       </x:c>
       <x:c r="E24" s="7" t="str">
         <x:v>Capacitors/Ceramic Capacitors</x:v>
       </x:c>
       <x:c r="F24" s="7" t="str">
-        <x:v>C_2_2uF_1206</x:v>
+        <x:v>C_10pF_0201</x:v>
       </x:c>
       <x:c r="G24" s="7" t="str">
-        <x:v>C_1206_3216Metric</x:v>
+        <x:v>ExternalDriver_0201-10pF-50V-10</x:v>
       </x:c>
       <x:c r="H24" s="7" t="str">
-        <x:v>2.2uF</x:v>
+        <x:v>10pF</x:v>
       </x:c>
       <x:c r="I24" s="7" t="str">
-        <x:v>1206</x:v>
+        <x:v>0201</x:v>
       </x:c>
       <x:c r="J24" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/23ccee80ee542e7cf156a772bb589942.pdf?productCode=C577211</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/1497a6a2cea2f2b0acf5e045d2bc193c.pdf?productCode=C561710</x:v>
       </x:c>
       <x:c r="K24" s="7" t="str"/>
       <x:c r="L24" s="7" t="str"/>
       <x:c r="M24" s="7" t="str">
-        <x:v>../datasheets/C577211/CC1206KKX7R0BB225.pdf</x:v>
+        <x:v>../datasheets/C561710/FN03N100J500PLG.pdf</x:v>
       </x:c>
       <x:c r="N24" s="7" t="str"/>
       <x:c r="O24" s="7" t="str">
-        <x:v>Active</x:v>
+        <x:v>OutOfStock</x:v>
       </x:c>
       <x:c r="P24" s="7" t="str">
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q24" s="7" t="str">
-        <x:v>C1206</x:v>
+        <x:v>0201-10pF-50V-10%</x:v>
       </x:c>
       <x:c r="R24" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C577211.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C561710.html</x:v>
       </x:c>
       <x:c r="S24" s="7" t="str">
-        <x:v>Package: 1206; Capacitance: 2.2uF; Temperature Coefficient: X7R; Tolerance: ±10%; Voltage Rating: 100V</x:v>
+        <x:v>Package: 0201; Capacitance: 10pF; Temperature Coefficient: C0G; Tolerance: ±5%; Voltage Rating: 50V</x:v>
       </x:c>
       <x:c r="T24" s="7" t="str">
-        <x:v>Designators: C12</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: C29,C32</x:v>
       </x:c>
       <x:c r="U24" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V24" s="7" t="str">
-        <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
+        <x:v>legacy_import</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="24" customHeight="1">
       <x:c r="A25" s="7" t="str">
-        <x:v>C596322</x:v>
+        <x:v>C561711</x:v>
       </x:c>
       <x:c r="B25" s="7" t="str">
-        <x:v>CC1206JKNPOZBN222</x:v>
+        <x:v>FN03N101J500PLG</x:v>
       </x:c>
       <x:c r="C25" s="7" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>PSA(信昌电陶)</x:v>
       </x:c>
       <x:c r="D25" s="7" t="str">
-        <x:v>2.2nF ±5% 630V Ceramic Capacitor NP0 1206</x:v>
+        <x:v>100pF 50V 5% 0201 ceramic capacitor</x:v>
       </x:c>
       <x:c r="E25" s="7" t="str">
         <x:v>Capacitors/Ceramic Capacitors</x:v>
       </x:c>
       <x:c r="F25" s="7" t="str">
-        <x:v>C_2_2nF_1206</x:v>
+        <x:v>C_100pF_0201</x:v>
       </x:c>
       <x:c r="G25" s="7" t="str">
-        <x:v>C_1206_3216Metric</x:v>
+        <x:v>C_0201_0603Metric</x:v>
       </x:c>
       <x:c r="H25" s="7" t="str">
-        <x:v>2.2nF</x:v>
+        <x:v>100pF</x:v>
       </x:c>
       <x:c r="I25" s="7" t="str">
-        <x:v>1206</x:v>
+        <x:v>0201</x:v>
       </x:c>
       <x:c r="J25" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/9a86cbae8c34c796174906a7ab23dad0.pdf?productCode=C596322</x:v>
+        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20241107/25D13BC56D84FBEC5B349398FCEBBC16.pdf</x:v>
       </x:c>
       <x:c r="K25" s="7" t="str"/>
       <x:c r="L25" s="7" t="str"/>
       <x:c r="M25" s="7" t="str">
-        <x:v>../datasheets/C596322/CC1206JKNPOZBN222.pdf</x:v>
+        <x:v>../datasheets/C561711/FN03N101J500PLG.pdf</x:v>
       </x:c>
       <x:c r="N25" s="7" t="str"/>
       <x:c r="O25" s="7" t="str">
@@ -7226,59 +7474,59 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q25" s="7" t="str">
-        <x:v>CC1206JKNPOZBN222</x:v>
+        <x:v>C0201</x:v>
       </x:c>
       <x:c r="R25" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C596322.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C561711.html</x:v>
       </x:c>
       <x:c r="S25" s="7" t="str">
-        <x:v>Package: 1206; Capacitance: 2.2nF; Temperature Coefficient: NP0; Tolerance: ±5%; Voltage Rating: 630V</x:v>
+        <x:v>Package: 0201; Capacitance: 100pF; Voltage: 50V; Tolerance: 5%</x:v>
       </x:c>
       <x:c r="T25" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: C14,C18</x:v>
+        <x:v>EBOM BOM_QS01_GD32F503_V1.10; designators C15/C16/C17/C20.</x:v>
       </x:c>
       <x:c r="U25" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V25" s="7" t="str">
-        <x:v>X200T_ECU_B1_V1.0_20240809; legacy_import</x:v>
+        <x:v>EBOM_V1.10</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="24" customHeight="1">
       <x:c r="A26" s="7" t="str">
-        <x:v>C60137</x:v>
+        <x:v>C576517</x:v>
       </x:c>
       <x:c r="B26" s="7" t="str">
-        <x:v>CC0402JRNPO9BN470</x:v>
+        <x:v>GRM32EC72A106KE05L</x:v>
       </x:c>
       <x:c r="C26" s="7" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>muRata</x:v>
       </x:c>
       <x:c r="D26" s="7" t="str">
-        <x:v>47pF ±5% 50V Ceramic Capacitor NP0 0402</x:v>
+        <x:v>10uF ±10% 100V Ceramic Capacitor X7S 1210</x:v>
       </x:c>
       <x:c r="E26" s="7" t="str">
         <x:v>Capacitors/Ceramic Capacitors</x:v>
       </x:c>
       <x:c r="F26" s="7" t="str">
-        <x:v>C_47pF_0402</x:v>
+        <x:v>C_10uF_1210</x:v>
       </x:c>
       <x:c r="G26" s="7" t="str">
-        <x:v>C_0402_1005Metric</x:v>
+        <x:v>C_1210_3225Metric</x:v>
       </x:c>
       <x:c r="H26" s="7" t="str">
-        <x:v>47pF</x:v>
+        <x:v>10uF</x:v>
       </x:c>
       <x:c r="I26" s="7" t="str">
-        <x:v>0402</x:v>
+        <x:v>1210</x:v>
       </x:c>
       <x:c r="J26" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/4eca2bb4b507f1633db47e922d632b95.pdf?productCode=C60137</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/a5661d5fbdf2b41a50853cb83d84d655.pdf?productCode=C576517</x:v>
       </x:c>
       <x:c r="K26" s="7" t="str"/>
       <x:c r="L26" s="7" t="str"/>
       <x:c r="M26" s="7" t="str">
-        <x:v>../datasheets/C60137/CC0402JRNPO9BN470.pdf</x:v>
+        <x:v>../datasheets/C576517/GRM32EC72A106KE05L.pdf</x:v>
       </x:c>
       <x:c r="N26" s="7" t="str"/>
       <x:c r="O26" s="7" t="str">
@@ -7288,16 +7536,16 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q26" s="7" t="str">
-        <x:v>C0402</x:v>
+        <x:v>C1210</x:v>
       </x:c>
       <x:c r="R26" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C60137.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C576517.html</x:v>
       </x:c>
       <x:c r="S26" s="7" t="str">
-        <x:v>Package: 0402; Capacitance: 47pF; Temperature Coefficient: NP0; Tolerance: ±5%; Voltage Rating: 50V</x:v>
+        <x:v>Package: 1210; Capacitance: 10uF; Temperature Coefficient: X7S; Tolerance: ±10%; Voltage Rating: 100V</x:v>
       </x:c>
       <x:c r="T26" s="7" t="str">
-        <x:v>Designators: C35</x:v>
+        <x:v>Designators: C2, C3, C5, C6, C7, C8, C17, C46, C47, C48, C81, C82, C83, C87, C88</x:v>
       </x:c>
       <x:c r="U26" s="7" t="str">
         <x:v>METADATA_READY</x:v>
@@ -7308,39 +7556,39 @@
     </x:row>
     <x:row r="27" ht="24" customHeight="1">
       <x:c r="A27" s="7" t="str">
-        <x:v>C668346</x:v>
+        <x:v>C577211</x:v>
       </x:c>
       <x:c r="B27" s="7" t="str">
-        <x:v>GRM033Z71C104KE14D</x:v>
+        <x:v>CC1206KKX7R0BB225</x:v>
       </x:c>
       <x:c r="C27" s="7" t="str">
-        <x:v>muRata</x:v>
+        <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D27" s="7" t="str">
-        <x:v>100nF ±10% 16V Ceramic Capacitor X7R 0201</x:v>
+        <x:v>2.2uF ±10% 100V Ceramic Capacitor X7R 1206</x:v>
       </x:c>
       <x:c r="E27" s="7" t="str">
         <x:v>Capacitors/Ceramic Capacitors</x:v>
       </x:c>
       <x:c r="F27" s="7" t="str">
-        <x:v>C_100nF_0201</x:v>
+        <x:v>C_2_2uF_1206</x:v>
       </x:c>
       <x:c r="G27" s="7" t="str">
-        <x:v>ExternalDriver_0201-100nF-16V-10</x:v>
+        <x:v>C_1206_3216Metric</x:v>
       </x:c>
       <x:c r="H27" s="7" t="str">
-        <x:v>100nF</x:v>
+        <x:v>2.2uF</x:v>
       </x:c>
       <x:c r="I27" s="7" t="str">
-        <x:v>0201</x:v>
+        <x:v>1206</x:v>
       </x:c>
       <x:c r="J27" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/0fb4604782167a586c3dd1f22396ac96.pdf?productCode=C668346</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/23ccee80ee542e7cf156a772bb589942.pdf?productCode=C577211</x:v>
       </x:c>
       <x:c r="K27" s="7" t="str"/>
       <x:c r="L27" s="7" t="str"/>
       <x:c r="M27" s="7" t="str">
-        <x:v>../datasheets/C668346/GRM033Z71C104KE14D.pdf</x:v>
+        <x:v>../datasheets/C577211/CC1206KKX7R0BB225.pdf</x:v>
       </x:c>
       <x:c r="N27" s="7" t="str"/>
       <x:c r="O27" s="7" t="str">
@@ -7350,117 +7598,121 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q27" s="7" t="str">
-        <x:v>0201-100nF-16V-10%</x:v>
+        <x:v>C1206</x:v>
       </x:c>
       <x:c r="R27" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C668346.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C577211.html</x:v>
       </x:c>
       <x:c r="S27" s="7" t="str">
-        <x:v>Package: 0201; Capacitance: 100nF; Temperature Coefficient: X7R; Tolerance: ±10%; Voltage Rating: 16V</x:v>
+        <x:v>Package: 1206; Capacitance: 2.2uF; Temperature Coefficient: X7R; Tolerance: ±10%; Voltage Rating: 100V</x:v>
       </x:c>
       <x:c r="T27" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls, BOM_PASTER_8984112A_Y189.xls; Designators: BOM_PASTER_8984112A_Y182.xls: C1,C6,C12,C13,C21,C26,C27,C30,C31,C33,C34,C38,C46,C47,C48,C49,C50,C54,C55,C58,C59,C60; BOM_PASTER_8984112A_Y185.xls: C1,C2,C3,C4,C6,C7,C9,C12,C14,C21,C24; BOM_PASTER_8984112A_Y189.xls: C1</x:v>
+        <x:v>Designators: C12</x:v>
       </x:c>
       <x:c r="U27" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V27" s="7" t="str">
-        <x:v>legacy_import</x:v>
+        <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="24" customHeight="1">
       <x:c r="A28" s="7" t="str">
-        <x:v>C730413</x:v>
+        <x:v>C596322</x:v>
       </x:c>
       <x:c r="B28" s="7" t="str">
-        <x:v>CL03C101JB3NNNC</x:v>
+        <x:v>CC1206JKNPOZBN222</x:v>
       </x:c>
       <x:c r="C28" s="7" t="str">
-        <x:v>Samsung Electro-Mechanics</x:v>
+        <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D28" s="7" t="str">
-        <x:v>100pF ±5% 50V Ceramic Capacitor C0G 0201</x:v>
+        <x:v>2.2nF ±5% 630V Ceramic Capacitor NP0 1206</x:v>
       </x:c>
       <x:c r="E28" s="7" t="str">
         <x:v>Capacitors/Ceramic Capacitors</x:v>
       </x:c>
       <x:c r="F28" s="7" t="str">
-        <x:v>C_100pF_0201</x:v>
+        <x:v>C_2_2nF_1206</x:v>
       </x:c>
       <x:c r="G28" s="7" t="str">
-        <x:v>ExternalDriver_0201-100pF-50V-5</x:v>
+        <x:v>C_1206_3216Metric</x:v>
       </x:c>
       <x:c r="H28" s="7" t="str">
-        <x:v>100pF</x:v>
+        <x:v>2.2nF</x:v>
       </x:c>
       <x:c r="I28" s="7" t="str">
-        <x:v>0201</x:v>
+        <x:v>1206</x:v>
       </x:c>
       <x:c r="J28" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/02336ea48ea44ca18c72517dd3cb7b47.pdf?productCode=C730413</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/9a86cbae8c34c796174906a7ab23dad0.pdf?productCode=C596322</x:v>
       </x:c>
       <x:c r="K28" s="7" t="str"/>
       <x:c r="L28" s="7" t="str"/>
       <x:c r="M28" s="7" t="str">
-        <x:v>../datasheets/C730413/CL03C101JB3NNNC.pdf</x:v>
+        <x:v>../datasheets/C596322/CC1206JKNPOZBN222.pdf</x:v>
       </x:c>
       <x:c r="N28" s="7" t="str"/>
       <x:c r="O28" s="7" t="str">
-        <x:v>OutOfStock</x:v>
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="P28" s="7" t="str">
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q28" s="7" t="str">
-        <x:v>0201-100pF-50V-5%</x:v>
+        <x:v>CC1206JKNPOZBN222</x:v>
       </x:c>
       <x:c r="R28" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C730413.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C596322.html</x:v>
       </x:c>
       <x:c r="S28" s="7" t="str">
-        <x:v>Package: 0201; Capacitance: 100pF; Temperature Coefficient: C0G; Tolerance: ±5%; Voltage Rating: 50V</x:v>
+        <x:v>Package: 1206; Capacitance: 2.2nF; Temperature Coefficient: NP0; Tolerance: ±5%; Voltage Rating: 630V</x:v>
       </x:c>
       <x:c r="T28" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y182.xls: C3,C4,C5,C9,C10,C11,C24,C35,C36,C37,C39,C40,C42,C43,C44,C45; BOM_PASTER_8984112A_Y185.xls: C18,C19,C20,C22</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: C14,C18</x:v>
       </x:c>
       <x:c r="U28" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V28" s="7" t="str">
-        <x:v>legacy_import</x:v>
+        <x:v>X200T_ECU_B1_V1.0_20240809; legacy_import</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="24" customHeight="1">
       <x:c r="A29" s="7" t="str">
-        <x:v>C730422</x:v>
+        <x:v>C60137</x:v>
       </x:c>
       <x:c r="B29" s="7" t="str">
-        <x:v>CL03Y104KO3NNNC</x:v>
+        <x:v>CC0402JRNPO9BN470</x:v>
       </x:c>
       <x:c r="C29" s="7" t="str">
-        <x:v>SAMSUNG</x:v>
+        <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D29" s="7" t="str">
-        <x:v>100nF ±10% 16V Ceramic Capacitor X7R</x:v>
+        <x:v>47pF ±5% 50V Ceramic Capacitor NP0 0402</x:v>
       </x:c>
       <x:c r="E29" s="7" t="str">
         <x:v>Capacitors/Ceramic Capacitors</x:v>
       </x:c>
-      <x:c r="F29" s="7" t="str"/>
-      <x:c r="G29" s="7" t="str"/>
+      <x:c r="F29" s="7" t="str">
+        <x:v>C_47pF_0402</x:v>
+      </x:c>
+      <x:c r="G29" s="7" t="str">
+        <x:v>C_0402_1005Metric</x:v>
+      </x:c>
       <x:c r="H29" s="7" t="str">
-        <x:v>100nF</x:v>
+        <x:v>47pF</x:v>
       </x:c>
       <x:c r="I29" s="7" t="str">
-        <x:v>0201</x:v>
+        <x:v>0402</x:v>
       </x:c>
       <x:c r="J29" s="7" t="str">
-        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20160218/1457707763339.pdf</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/4eca2bb4b507f1633db47e922d632b95.pdf?productCode=C60137</x:v>
       </x:c>
       <x:c r="K29" s="7" t="str"/>
       <x:c r="L29" s="7" t="str"/>
       <x:c r="M29" s="7" t="str">
-        <x:v>../datasheets/C730422/CL03Y104KO3NNNC.pdf</x:v>
+        <x:v>../datasheets/C60137/CC0402JRNPO9BN470.pdf</x:v>
       </x:c>
       <x:c r="N29" s="7" t="str"/>
       <x:c r="O29" s="7" t="str">
@@ -7470,59 +7722,59 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q29" s="7" t="str">
-        <x:v>0201-100nF-16V-10%</x:v>
+        <x:v>C0402</x:v>
       </x:c>
       <x:c r="R29" s="7" t="str">
-        <x:v>https://item.szlcsc.com/778821.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C60137.html</x:v>
       </x:c>
       <x:c r="S29" s="7" t="str">
-        <x:v>Package: 0201; Capacitance: 100nF; Tolerance: ±10%; Voltage Rating: 16V; Temperature Coefficient: X7R</x:v>
+        <x:v>Package: 0402; Capacitance: 47pF; Temperature Coefficient: NP0; Tolerance: ±5%; Voltage Rating: 50V</x:v>
       </x:c>
       <x:c r="T29" s="7" t="str">
-        <x:v>Designators: Y43-C17; Z300BL-C17</x:v>
+        <x:v>Designators: C35</x:v>
       </x:c>
       <x:c r="U29" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V29" s="7" t="str">
-        <x:v>Y43; Z300BL</x:v>
+        <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="24" customHeight="1">
       <x:c r="A30" s="7" t="str">
-        <x:v>C76941</x:v>
+        <x:v>C668346</x:v>
       </x:c>
       <x:c r="B30" s="7" t="str">
-        <x:v>GRM033R71A103KA01D</x:v>
+        <x:v>GRM033Z71C104KE14D</x:v>
       </x:c>
       <x:c r="C30" s="7" t="str">
         <x:v>muRata</x:v>
       </x:c>
       <x:c r="D30" s="7" t="str">
-        <x:v>10nF ±10% 10V Ceramic Capacitor X7R 0201</x:v>
+        <x:v>100nF ±10% 16V Ceramic Capacitor X7R 0201</x:v>
       </x:c>
       <x:c r="E30" s="7" t="str">
         <x:v>Capacitors/Ceramic Capacitors</x:v>
       </x:c>
       <x:c r="F30" s="7" t="str">
-        <x:v>C_10nF_0201</x:v>
+        <x:v>C_100nF_0201</x:v>
       </x:c>
       <x:c r="G30" s="7" t="str">
-        <x:v>ExternalDriver_0201-10nF-10V-10</x:v>
+        <x:v>ExternalDriver_0201-100nF-16V-10</x:v>
       </x:c>
       <x:c r="H30" s="7" t="str">
-        <x:v>10nF</x:v>
+        <x:v>100nF</x:v>
       </x:c>
       <x:c r="I30" s="7" t="str">
         <x:v>0201</x:v>
       </x:c>
       <x:c r="J30" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/58a7d404c3534585b4a0e91caba788f7.pdf?productCode=C76941</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/0fb4604782167a586c3dd1f22396ac96.pdf?productCode=C668346</x:v>
       </x:c>
       <x:c r="K30" s="7" t="str"/>
       <x:c r="L30" s="7" t="str"/>
       <x:c r="M30" s="7" t="str">
-        <x:v>../datasheets/C76941/GRM033R71A103KA01D.pdf</x:v>
+        <x:v>../datasheets/C668346/GRM033Z71C104KE14D.pdf</x:v>
       </x:c>
       <x:c r="N30" s="7" t="str"/>
       <x:c r="O30" s="7" t="str">
@@ -7532,16 +7784,16 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q30" s="7" t="str">
-        <x:v>0201-10nF-10V-10%</x:v>
+        <x:v>0201-100nF-16V-10%</x:v>
       </x:c>
       <x:c r="R30" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C76941.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C668346.html</x:v>
       </x:c>
       <x:c r="S30" s="7" t="str">
-        <x:v>Package: 0201; Capacitance: 10nF; Temperature Coefficient: X7R; Tolerance: ±10%; Voltage Rating: 10V</x:v>
+        <x:v>Package: 0201; Capacitance: 100nF; Temperature Coefficient: X7R; Tolerance: ±10%; Voltage Rating: 16V</x:v>
       </x:c>
       <x:c r="T30" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y185.xls: C10</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls, BOM_PASTER_8984112A_Y189.xls; Designators: BOM_PASTER_8984112A_Y182.xls: C1,C6,C12,C13,C21,C26,C27,C30,C31,C33,C34,C38,C46,C47,C48,C49,C50,C54,C55,C58,C59,C60; BOM_PASTER_8984112A_Y185.xls: C1,C2,C3,C4,C6,C7,C9,C12,C14,C21,C24; BOM_PASTER_8984112A_Y189.xls: C1</x:v>
       </x:c>
       <x:c r="U30" s="7" t="str">
         <x:v>METADATA_READY</x:v>
@@ -7552,39 +7804,39 @@
     </x:row>
     <x:row r="31" ht="24" customHeight="1">
       <x:c r="A31" s="7" t="str">
-        <x:v>C77020</x:v>
+        <x:v>C694230</x:v>
       </x:c>
       <x:c r="B31" s="7" t="str">
-        <x:v>GRM155R71H104KE14D</x:v>
+        <x:v>CGA4J1X7S1E106KT0Y0N</x:v>
       </x:c>
       <x:c r="C31" s="7" t="str">
-        <x:v>muRata</x:v>
+        <x:v>TDK</x:v>
       </x:c>
       <x:c r="D31" s="7" t="str">
-        <x:v>100nF ±10% 50V Ceramic Capacitor X7R 0402</x:v>
+        <x:v>10uF 25V X7S 0805 ceramic capacitor</x:v>
       </x:c>
       <x:c r="E31" s="7" t="str">
         <x:v>Capacitors/Ceramic Capacitors</x:v>
       </x:c>
       <x:c r="F31" s="7" t="str">
-        <x:v>C_100nF_0402</x:v>
+        <x:v>C_10uF_0805</x:v>
       </x:c>
       <x:c r="G31" s="7" t="str">
-        <x:v>C_0402_1005Metric</x:v>
+        <x:v>C_0805_2012Metric</x:v>
       </x:c>
       <x:c r="H31" s="7" t="str">
-        <x:v>100nF</x:v>
+        <x:v>10uF</x:v>
       </x:c>
       <x:c r="I31" s="7" t="str">
-        <x:v>0402</x:v>
+        <x:v>0805</x:v>
       </x:c>
       <x:c r="J31" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/64ac52ef9cc4e1905eba7e2ece85e662.pdf?productCode=C77020</x:v>
+        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20200407/C342975_AB13C551805E4B495BBDB585D2C58CA0.pdf</x:v>
       </x:c>
       <x:c r="K31" s="7" t="str"/>
       <x:c r="L31" s="7" t="str"/>
       <x:c r="M31" s="7" t="str">
-        <x:v>../datasheets/C77020/GRM155R71H104KE14D.pdf</x:v>
+        <x:v>../datasheets/C694230/CGA4J1X7S1E106KT0Y0N.pdf</x:v>
       </x:c>
       <x:c r="N31" s="7" t="str"/>
       <x:c r="O31" s="7" t="str">
@@ -7594,31 +7846,275 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q31" s="7" t="str">
+        <x:v>C0805</x:v>
+      </x:c>
+      <x:c r="R31" s="7" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C694230.html</x:v>
+      </x:c>
+      <x:c r="S31" s="7" t="str">
+        <x:v>Package: 0805; Capacitance: 10uF; Voltage: 25V; Tolerance: 10%; Temperature Coefficient: X7S</x:v>
+      </x:c>
+      <x:c r="T31" s="7" t="str">
+        <x:v>EBOM BOM_QS01_GD32F503_V1.10; designator C18.</x:v>
+      </x:c>
+      <x:c r="U31" s="7" t="str">
+        <x:v>METADATA_READY</x:v>
+      </x:c>
+      <x:c r="V31" s="7" t="str">
+        <x:v>EBOM_V1.10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="24" customHeight="1">
+      <x:c r="A32" s="7" t="str">
+        <x:v>C730413</x:v>
+      </x:c>
+      <x:c r="B32" s="7" t="str">
+        <x:v>CL03C101JB3NNNC</x:v>
+      </x:c>
+      <x:c r="C32" s="7" t="str">
+        <x:v>Samsung Electro-Mechanics</x:v>
+      </x:c>
+      <x:c r="D32" s="7" t="str">
+        <x:v>100pF ±5% 50V Ceramic Capacitor C0G 0201</x:v>
+      </x:c>
+      <x:c r="E32" s="7" t="str">
+        <x:v>Capacitors/Ceramic Capacitors</x:v>
+      </x:c>
+      <x:c r="F32" s="7" t="str">
+        <x:v>C_100pF_0201</x:v>
+      </x:c>
+      <x:c r="G32" s="7" t="str">
+        <x:v>ExternalDriver_0201-100pF-50V-5</x:v>
+      </x:c>
+      <x:c r="H32" s="7" t="str">
+        <x:v>100pF</x:v>
+      </x:c>
+      <x:c r="I32" s="7" t="str">
+        <x:v>0201</x:v>
+      </x:c>
+      <x:c r="J32" s="7" t="str">
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/02336ea48ea44ca18c72517dd3cb7b47.pdf?productCode=C730413</x:v>
+      </x:c>
+      <x:c r="K32" s="7" t="str"/>
+      <x:c r="L32" s="7" t="str"/>
+      <x:c r="M32" s="7" t="str">
+        <x:v>../datasheets/C730413/CL03C101JB3NNNC.pdf</x:v>
+      </x:c>
+      <x:c r="N32" s="7" t="str"/>
+      <x:c r="O32" s="7" t="str">
+        <x:v>OutOfStock</x:v>
+      </x:c>
+      <x:c r="P32" s="7" t="str">
+        <x:v>LCSC</x:v>
+      </x:c>
+      <x:c r="Q32" s="7" t="str">
+        <x:v>0201-100pF-50V-5%</x:v>
+      </x:c>
+      <x:c r="R32" s="7" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C730413.html</x:v>
+      </x:c>
+      <x:c r="S32" s="7" t="str">
+        <x:v>Package: 0201; Capacitance: 100pF; Temperature Coefficient: C0G; Tolerance: ±5%; Voltage Rating: 50V</x:v>
+      </x:c>
+      <x:c r="T32" s="7" t="str">
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y182.xls: C3,C4,C5,C9,C10,C11,C24,C35,C36,C37,C39,C40,C42,C43,C44,C45; BOM_PASTER_8984112A_Y185.xls: C18,C19,C20,C22</x:v>
+      </x:c>
+      <x:c r="U32" s="7" t="str">
+        <x:v>METADATA_READY</x:v>
+      </x:c>
+      <x:c r="V32" s="7" t="str">
+        <x:v>legacy_import</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="24" customHeight="1">
+      <x:c r="A33" s="7" t="str">
+        <x:v>C730422</x:v>
+      </x:c>
+      <x:c r="B33" s="7" t="str">
+        <x:v>CL03Y104KO3NNNC</x:v>
+      </x:c>
+      <x:c r="C33" s="7" t="str">
+        <x:v>SAMSUNG</x:v>
+      </x:c>
+      <x:c r="D33" s="7" t="str">
+        <x:v>100nF ±10% 16V Ceramic Capacitor X7R</x:v>
+      </x:c>
+      <x:c r="E33" s="7" t="str">
+        <x:v>Capacitors/Ceramic Capacitors</x:v>
+      </x:c>
+      <x:c r="F33" s="7" t="str"/>
+      <x:c r="G33" s="7" t="str"/>
+      <x:c r="H33" s="7" t="str">
+        <x:v>100nF</x:v>
+      </x:c>
+      <x:c r="I33" s="7" t="str">
+        <x:v>0201</x:v>
+      </x:c>
+      <x:c r="J33" s="7" t="str">
+        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20160218/1457707763339.pdf</x:v>
+      </x:c>
+      <x:c r="K33" s="7" t="str"/>
+      <x:c r="L33" s="7" t="str"/>
+      <x:c r="M33" s="7" t="str">
+        <x:v>../datasheets/C730422/CL03Y104KO3NNNC.pdf</x:v>
+      </x:c>
+      <x:c r="N33" s="7" t="str"/>
+      <x:c r="O33" s="7" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="P33" s="7" t="str">
+        <x:v>LCSC</x:v>
+      </x:c>
+      <x:c r="Q33" s="7" t="str">
+        <x:v>0201-100nF-16V-10%</x:v>
+      </x:c>
+      <x:c r="R33" s="7" t="str">
+        <x:v>https://item.szlcsc.com/778821.html</x:v>
+      </x:c>
+      <x:c r="S33" s="7" t="str">
+        <x:v>Package: 0201; Capacitance: 100nF; Tolerance: ±10%; Voltage Rating: 16V; Temperature Coefficient: X7R</x:v>
+      </x:c>
+      <x:c r="T33" s="7" t="str">
+        <x:v>Designators: Y43-C17; Z300BL-C17</x:v>
+      </x:c>
+      <x:c r="U33" s="7" t="str">
+        <x:v>METADATA_READY</x:v>
+      </x:c>
+      <x:c r="V33" s="7" t="str">
+        <x:v>Y43; Z300BL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="24" customHeight="1">
+      <x:c r="A34" s="7" t="str">
+        <x:v>C76941</x:v>
+      </x:c>
+      <x:c r="B34" s="7" t="str">
+        <x:v>GRM033R71A103KA01D</x:v>
+      </x:c>
+      <x:c r="C34" s="7" t="str">
+        <x:v>muRata</x:v>
+      </x:c>
+      <x:c r="D34" s="7" t="str">
+        <x:v>10nF ±10% 10V Ceramic Capacitor X7R 0201</x:v>
+      </x:c>
+      <x:c r="E34" s="7" t="str">
+        <x:v>Capacitors/Ceramic Capacitors</x:v>
+      </x:c>
+      <x:c r="F34" s="7" t="str">
+        <x:v>C_10nF_0201</x:v>
+      </x:c>
+      <x:c r="G34" s="7" t="str">
+        <x:v>ExternalDriver_0201-10nF-10V-10</x:v>
+      </x:c>
+      <x:c r="H34" s="7" t="str">
+        <x:v>10nF</x:v>
+      </x:c>
+      <x:c r="I34" s="7" t="str">
+        <x:v>0201</x:v>
+      </x:c>
+      <x:c r="J34" s="7" t="str">
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/58a7d404c3534585b4a0e91caba788f7.pdf?productCode=C76941</x:v>
+      </x:c>
+      <x:c r="K34" s="7" t="str"/>
+      <x:c r="L34" s="7" t="str"/>
+      <x:c r="M34" s="7" t="str">
+        <x:v>../datasheets/C76941/GRM033R71A103KA01D.pdf</x:v>
+      </x:c>
+      <x:c r="N34" s="7" t="str"/>
+      <x:c r="O34" s="7" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="P34" s="7" t="str">
+        <x:v>LCSC</x:v>
+      </x:c>
+      <x:c r="Q34" s="7" t="str">
+        <x:v>0201-10nF-10V-10%</x:v>
+      </x:c>
+      <x:c r="R34" s="7" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C76941.html</x:v>
+      </x:c>
+      <x:c r="S34" s="7" t="str">
+        <x:v>Package: 0201; Capacitance: 10nF; Temperature Coefficient: X7R; Tolerance: ±10%; Voltage Rating: 10V</x:v>
+      </x:c>
+      <x:c r="T34" s="7" t="str">
+        <x:v>Sources: BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y185.xls: C10</x:v>
+      </x:c>
+      <x:c r="U34" s="7" t="str">
+        <x:v>METADATA_READY</x:v>
+      </x:c>
+      <x:c r="V34" s="7" t="str">
+        <x:v>legacy_import</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="24" customHeight="1">
+      <x:c r="A35" s="7" t="str">
+        <x:v>C77020</x:v>
+      </x:c>
+      <x:c r="B35" s="7" t="str">
+        <x:v>GRM155R71H104KE14D</x:v>
+      </x:c>
+      <x:c r="C35" s="7" t="str">
+        <x:v>muRata</x:v>
+      </x:c>
+      <x:c r="D35" s="7" t="str">
+        <x:v>100nF ±10% 50V Ceramic Capacitor X7R 0402</x:v>
+      </x:c>
+      <x:c r="E35" s="7" t="str">
+        <x:v>Capacitors/Ceramic Capacitors</x:v>
+      </x:c>
+      <x:c r="F35" s="7" t="str">
+        <x:v>C_100nF_0402</x:v>
+      </x:c>
+      <x:c r="G35" s="7" t="str">
+        <x:v>C_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="H35" s="7" t="str">
+        <x:v>100nF</x:v>
+      </x:c>
+      <x:c r="I35" s="7" t="str">
+        <x:v>0402</x:v>
+      </x:c>
+      <x:c r="J35" s="7" t="str">
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/64ac52ef9cc4e1905eba7e2ece85e662.pdf?productCode=C77020</x:v>
+      </x:c>
+      <x:c r="K35" s="7" t="str"/>
+      <x:c r="L35" s="7" t="str"/>
+      <x:c r="M35" s="7" t="str">
+        <x:v>../datasheets/C77020/GRM155R71H104KE14D.pdf</x:v>
+      </x:c>
+      <x:c r="N35" s="7" t="str"/>
+      <x:c r="O35" s="7" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="P35" s="7" t="str">
+        <x:v>LCSC</x:v>
+      </x:c>
+      <x:c r="Q35" s="7" t="str">
         <x:v>C0402</x:v>
       </x:c>
-      <x:c r="R31" s="7" t="str">
+      <x:c r="R35" s="7" t="str">
         <x:v>https://www.lcsc.com/product-detail/C77020.html</x:v>
       </x:c>
-      <x:c r="S31" s="7" t="str">
+      <x:c r="S35" s="7" t="str">
         <x:v>Package: 0402; Capacitance: 100nF; Temperature Coefficient: X7R; Tolerance: ±10%; Voltage Rating: 50V</x:v>
       </x:c>
-      <x:c r="T31" s="7" t="str">
+      <x:c r="T35" s="7" t="str">
         <x:v>Designators: C10, C18, C19, C20, C23, C24, C25, C26, C30, C32, C34, C36, C38, C39, C40, C41, C42, C43, C44, C50, C51, C72, C77, C78</x:v>
       </x:c>
-      <x:c r="U31" s="7" t="str">
-        <x:v>METADATA_READY</x:v>
-      </x:c>
-      <x:c r="V31" s="7" t="str">
+      <x:c r="U35" s="7" t="str">
+        <x:v>METADATA_READY</x:v>
+      </x:c>
+      <x:c r="V35" s="7" t="str">
         <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="U5:U31">
+  <x:conditionalFormatting sqref="U5:U35">
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="CLASSIFIED_PARTIAL"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc22264051814921"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd3080de32534f29"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8227,7 +8723,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra175c7cadaf54996"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a18507ab2e24e53"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8267,7 +8763,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="2" t="str">
-        <x:v>类别：Circuit Protection；记录数：1；来源：all_parts.csv</x:v>
+        <x:v>类别：Circuit Protection；记录数：2；来源：all_parts.csv</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -8340,39 +8836,39 @@
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
       <x:c r="A5" s="7" t="str">
-        <x:v>C54582078</x:v>
+        <x:v>C123805</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>SLESD11LE5.0C</x:v>
+        <x:v>SMF16CA</x:v>
       </x:c>
       <x:c r="C5" s="7" t="str">
-        <x:v>Slkor(萨科微)</x:v>
+        <x:v>MDD(辰达半导体)</x:v>
       </x:c>
       <x:c r="D5" s="7" t="str">
-        <x:v>0.3pF 5V bidirectional ESD protection diode, DFN0603-2L</x:v>
+        <x:v>16V 200W bidirectional TVS diode SOD-123FL</x:v>
       </x:c>
       <x:c r="E5" s="7" t="str">
-        <x:v>Circuit Protection/ESD Protection</x:v>
+        <x:v>Circuit Protection/TVS Diodes</x:v>
       </x:c>
       <x:c r="F5" s="7" t="str">
-        <x:v>SLESD11LE5.0C</x:v>
+        <x:v>SMF16CA</x:v>
       </x:c>
       <x:c r="G5" s="7" t="str">
-        <x:v>D_0201_0603Metric</x:v>
+        <x:v>D_SOD-123F</x:v>
       </x:c>
       <x:c r="H5" s="7" t="str">
-        <x:v>SLESD11LE5.0C</x:v>
+        <x:v>SMF16CA</x:v>
       </x:c>
       <x:c r="I5" s="7" t="str">
-        <x:v>DFN0603-2L</x:v>
+        <x:v>SOD-123FL</x:v>
       </x:c>
       <x:c r="J5" s="7" t="str">
-        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20260407/8CFBFE2B8741D426B78BD31A162E1949.pdf</x:v>
+        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20250911/A9E208B97C1B87827444A0C468124C54.pdf</x:v>
       </x:c>
       <x:c r="K5" s="7" t="str"/>
       <x:c r="L5" s="7" t="str"/>
       <x:c r="M5" s="7" t="str">
-        <x:v>../datasheets/C54582078/SLESD11LE5.0C.pdf</x:v>
+        <x:v>../datasheets/C123805/SMF16CA.pdf</x:v>
       </x:c>
       <x:c r="N5" s="7" t="str"/>
       <x:c r="O5" s="7" t="str">
@@ -8382,31 +8878,93 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q5" s="7" t="str">
+        <x:v>SOD-123FL</x:v>
+      </x:c>
+      <x:c r="R5" s="7" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C123805.html</x:v>
+      </x:c>
+      <x:c r="S5" s="7" t="str">
+        <x:v>Package: SOD-123FL; Reverse Stand-Off Voltage: 16V; Peak Pulse Power: 200W; Polarity: Bidirectional</x:v>
+      </x:c>
+      <x:c r="T5" s="7" t="str">
+        <x:v>EBOM BOM_QS01_GD32F503_V1.10; designator D3.</x:v>
+      </x:c>
+      <x:c r="U5" s="7" t="str">
+        <x:v>METADATA_READY</x:v>
+      </x:c>
+      <x:c r="V5" s="7" t="str">
+        <x:v>EBOM_V1.10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="24" customHeight="1">
+      <x:c r="A6" s="7" t="str">
+        <x:v>C54582078</x:v>
+      </x:c>
+      <x:c r="B6" s="7" t="str">
+        <x:v>SLESD11LE5.0C</x:v>
+      </x:c>
+      <x:c r="C6" s="7" t="str">
+        <x:v>Slkor(萨科微)</x:v>
+      </x:c>
+      <x:c r="D6" s="7" t="str">
+        <x:v>0.3pF 5V bidirectional ESD protection diode, DFN0603-2L</x:v>
+      </x:c>
+      <x:c r="E6" s="7" t="str">
+        <x:v>Circuit Protection/ESD Protection</x:v>
+      </x:c>
+      <x:c r="F6" s="7" t="str">
+        <x:v>SLESD11LE5.0C</x:v>
+      </x:c>
+      <x:c r="G6" s="7" t="str">
+        <x:v>D_0201_0603Metric</x:v>
+      </x:c>
+      <x:c r="H6" s="7" t="str">
+        <x:v>SLESD11LE5.0C</x:v>
+      </x:c>
+      <x:c r="I6" s="7" t="str">
         <x:v>DFN0603-2L</x:v>
       </x:c>
-      <x:c r="R5" s="7" t="str">
+      <x:c r="J6" s="7" t="str">
+        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20260407/8CFBFE2B8741D426B78BD31A162E1949.pdf</x:v>
+      </x:c>
+      <x:c r="K6" s="7" t="str"/>
+      <x:c r="L6" s="7" t="str"/>
+      <x:c r="M6" s="7" t="str">
+        <x:v>../datasheets/C54582078/SLESD11LE5.0C.pdf</x:v>
+      </x:c>
+      <x:c r="N6" s="7" t="str"/>
+      <x:c r="O6" s="7" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="P6" s="7" t="str">
+        <x:v>LCSC</x:v>
+      </x:c>
+      <x:c r="Q6" s="7" t="str">
+        <x:v>DFN0603-2L</x:v>
+      </x:c>
+      <x:c r="R6" s="7" t="str">
         <x:v>https://www.lcsc.com/product-detail/C54582078.html</x:v>
       </x:c>
-      <x:c r="S5" s="7" t="str">
+      <x:c r="S6" s="7" t="str">
         <x:v>Package: DFN0603-2L; Reverse Stand-Off Voltage: 5.0V; Capacitance: 0.3pF; Peak Pulse Current: 5.5A; ESD: ±30kV</x:v>
       </x:c>
-      <x:c r="T5" s="7" t="str">
+      <x:c r="T6" s="7" t="str">
         <x:v>Requested ESD diode; replaces legacy placeholder C9900301658.</x:v>
       </x:c>
-      <x:c r="U5" s="7" t="str">
-        <x:v>METADATA_READY</x:v>
-      </x:c>
-      <x:c r="V5" s="7" t="str">
+      <x:c r="U6" s="7" t="str">
+        <x:v>METADATA_READY</x:v>
+      </x:c>
+      <x:c r="V6" s="7" t="str">
         <x:v>LocalParts</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="U5:U5">
+  <x:conditionalFormatting sqref="U5:U6">
     <x:cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="CLASSIFIED_PARTIAL"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb906408263684a76"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91780ab91e254bda"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8446,7 +9004,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="2" t="str">
-        <x:v>类别：Connectors；记录数：7；来源：all_parts.csv</x:v>
+        <x:v>类别：Connectors；记录数：8；来源：all_parts.csv</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -8703,39 +9261,39 @@
     </x:row>
     <x:row r="8" ht="24" customHeight="1">
       <x:c r="A8" s="7" t="str">
-        <x:v>C2937625</x:v>
+        <x:v>C2925430</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
-        <x:v>PZ254V-11-03P</x:v>
+        <x:v>BM29B0.6-2DS/2-0.35V</x:v>
       </x:c>
       <x:c r="C8" s="7" t="str">
-        <x:v>XFCN</x:v>
+        <x:v>HRS(广濑)</x:v>
       </x:c>
       <x:c r="D8" s="7" t="str">
-        <x:v>Pin Header 3 Position 2.54mm Pitch Single Row Through Hole -40℃~+105℃</x:v>
+        <x:v>4-pin 0.35mm pitch board-to-board connector</x:v>
       </x:c>
       <x:c r="E8" s="7" t="str">
         <x:v>Connectors/Headers, Male Pins</x:v>
       </x:c>
       <x:c r="F8" s="7" t="str">
-        <x:v>PZ254V-11-03P</x:v>
+        <x:v>BM29B0.6-2DS_2-0.35V</x:v>
       </x:c>
       <x:c r="G8" s="7" t="str">
-        <x:v>ExternalDriver_</x:v>
+        <x:v>BM29B0.6-2DS_2-0.35V</x:v>
       </x:c>
       <x:c r="H8" s="7" t="str">
-        <x:v>10</x:v>
+        <x:v>BM29B0.6-2DS/2-0.35V</x:v>
       </x:c>
       <x:c r="I8" s="7" t="str">
-        <x:v>Through Hole,P=2.54mm</x:v>
+        <x:v>SMD,P=0.35mm</x:v>
       </x:c>
       <x:c r="J8" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/3b85a1cdf6ed945f2e278f00c1e42442.pdf?productCode=C2937625</x:v>
+        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20211126/440829653A41B2C50D4B12C1CE909750.pdf</x:v>
       </x:c>
       <x:c r="K8" s="7" t="str"/>
       <x:c r="L8" s="7" t="str"/>
       <x:c r="M8" s="7" t="str">
-        <x:v>../datasheets/C2937625/PZ254V-11-03P.pdf</x:v>
+        <x:v>../datasheets/C2925430/BM29B0.6-2DS_2-0.35V.pdf</x:v>
       </x:c>
       <x:c r="N8" s="7" t="str"/>
       <x:c r="O8" s="7" t="str">
@@ -8745,59 +9303,59 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str">
-        <x:v>烧录口</x:v>
+        <x:v>SMD,P=0.35mm</x:v>
       </x:c>
       <x:c r="R8" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C2937625.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C2925430.html</x:v>
       </x:c>
       <x:c r="S8" s="7" t="str">
-        <x:v>Package: Through Hole,P=2.54mm; Connector Type: Through Hole; Voltage Rating (Max): 250V; Contact Material: Brass; Number of Rows: 1; Pitch: 2.54mm; Circluar Pins/Square Pins: Square pin; Current Rating: 3A; Supplementary Features: -; Insulation Height: 2.5mm; Length of Mating Pin: 6.1mm; Contact Plating: Gold; Number of PINs: 3P; Operating Temperature: -40℃~+105℃; Length of End Connection Pin: 3mm; Color: Black; Row Spacing: -; Pin Structure: 1x3P</x:v>
+        <x:v>Package: SMD; Pitch: 0.35mm; Pins: 4</x:v>
       </x:c>
       <x:c r="T8" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: J3</x:v>
+        <x:v>EBOM BOM_QS01_GD32F503_V1.10; designator J2.</x:v>
       </x:c>
       <x:c r="U8" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V8" s="7" t="str">
-        <x:v>legacy_import</x:v>
+        <x:v>EBOM_V1.10</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="24" customHeight="1">
       <x:c r="A9" s="7" t="str">
-        <x:v>C492420</x:v>
+        <x:v>C2937625</x:v>
       </x:c>
       <x:c r="B9" s="7" t="str">
-        <x:v>PZ254V-12-6P</x:v>
+        <x:v>PZ254V-11-03P</x:v>
       </x:c>
       <x:c r="C9" s="7" t="str">
         <x:v>XFCN</x:v>
       </x:c>
       <x:c r="D9" s="7" t="str">
-        <x:v>Pin Header 6 Position 2.54mm Pitch Dual Row Through Hole -40℃~+105℃</x:v>
+        <x:v>Pin Header 3 Position 2.54mm Pitch Single Row Through Hole -40℃~+105℃</x:v>
       </x:c>
       <x:c r="E9" s="7" t="str">
         <x:v>Connectors/Headers, Male Pins</x:v>
       </x:c>
       <x:c r="F9" s="7" t="str">
-        <x:v>PZ254V-12-6P</x:v>
+        <x:v>PZ254V-11-03P</x:v>
       </x:c>
       <x:c r="G9" s="7" t="str">
-        <x:v>ExternalDriver_6PIN</x:v>
+        <x:v>ExternalDriver_</x:v>
       </x:c>
       <x:c r="H9" s="7" t="str">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="I9" s="7" t="str">
         <x:v>Through Hole,P=2.54mm</x:v>
       </x:c>
       <x:c r="J9" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/50ec9710cee52ae98bff43fbb8887c5b.pdf?productCode=C492420</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/3b85a1cdf6ed945f2e278f00c1e42442.pdf?productCode=C2937625</x:v>
       </x:c>
       <x:c r="K9" s="7" t="str"/>
       <x:c r="L9" s="7" t="str"/>
       <x:c r="M9" s="7" t="str">
-        <x:v>../datasheets/C492420/PZ254V-12-6P.pdf</x:v>
+        <x:v>../datasheets/C2937625/PZ254V-11-03P.pdf</x:v>
       </x:c>
       <x:c r="N9" s="7" t="str"/>
       <x:c r="O9" s="7" t="str">
@@ -8807,16 +9365,16 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q9" s="7" t="str">
-        <x:v>6PIN烧录孔</x:v>
+        <x:v>烧录口</x:v>
       </x:c>
       <x:c r="R9" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C492420.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C2937625.html</x:v>
       </x:c>
       <x:c r="S9" s="7" t="str">
-        <x:v>Package: Through Hole,P=2.54mm; Connector Type: Through Hole; Voltage Rating (Max): -; Contact Material: Brass; Number of Rows: 2; Pitch: 2.54mm; Circluar Pins/Square Pins: Square pin; Current Rating: 3A; Insulation Height: 2.5mm; Length of Mating Pin: 6mm; Number of PINs: 6P; Operating Temperature: -40℃~+105℃; Length of End Connection Pin: 3mm; Contact Plating: Gold; Color: Black; Pin Structure: 2x3P; Row Spacing: 2.54mm</x:v>
+        <x:v>Package: Through Hole,P=2.54mm; Connector Type: Through Hole; Voltage Rating (Max): 250V; Contact Material: Brass; Number of Rows: 1; Pitch: 2.54mm; Circluar Pins/Square Pins: Square pin; Current Rating: 3A; Supplementary Features: -; Insulation Height: 2.5mm; Length of Mating Pin: 6.1mm; Contact Plating: Gold; Number of PINs: 3P; Operating Temperature: -40℃~+105℃; Length of End Connection Pin: 3mm; Color: Black; Row Spacing: -; Pin Structure: 1x3P</x:v>
       </x:c>
       <x:c r="T9" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: J8</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: J3</x:v>
       </x:c>
       <x:c r="U9" s="7" t="str">
         <x:v>METADATA_READY</x:v>
@@ -8827,39 +9385,39 @@
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
       <x:c r="A10" s="7" t="str">
-        <x:v>C5138889</x:v>
+        <x:v>C492420</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>GPCA101-0502A001C1AA</x:v>
+        <x:v>PZ254V-12-6P</x:v>
       </x:c>
       <x:c r="C10" s="7" t="str">
-        <x:v>GREENCONN</x:v>
+        <x:v>XFCN</x:v>
       </x:c>
       <x:c r="D10" s="7" t="str">
-        <x:v>Pin Header 5 Position 1mm Pitch Single Row Through Hole -40℃~+105℃</x:v>
+        <x:v>Pin Header 6 Position 2.54mm Pitch Dual Row Through Hole -40℃~+105℃</x:v>
       </x:c>
       <x:c r="E10" s="7" t="str">
         <x:v>Connectors/Headers, Male Pins</x:v>
       </x:c>
       <x:c r="F10" s="7" t="str">
-        <x:v>GPCA101-0502A001C1AA</x:v>
+        <x:v>PZ254V-12-6P</x:v>
       </x:c>
       <x:c r="G10" s="7" t="str">
-        <x:v>ExternalDriver_</x:v>
+        <x:v>ExternalDriver_6PIN</x:v>
       </x:c>
       <x:c r="H10" s="7" t="str">
-        <x:v>GPCA101-0502A</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="I10" s="7" t="str">
-        <x:v>Through Hole,P=1mm</x:v>
+        <x:v>Through Hole,P=2.54mm</x:v>
       </x:c>
       <x:c r="J10" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/9791ba8c859df0647813150b8f9162a2.pdf?productCode=C5138889</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/50ec9710cee52ae98bff43fbb8887c5b.pdf?productCode=C492420</x:v>
       </x:c>
       <x:c r="K10" s="7" t="str"/>
       <x:c r="L10" s="7" t="str"/>
       <x:c r="M10" s="7" t="str">
-        <x:v>../datasheets/C5138889/GPCA101-0502A001C1AA.pdf</x:v>
+        <x:v>../datasheets/C492420/PZ254V-12-6P.pdf</x:v>
       </x:c>
       <x:c r="N10" s="7" t="str"/>
       <x:c r="O10" s="7" t="str">
@@ -8869,16 +9427,16 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str">
-        <x:v>插件</x:v>
+        <x:v>6PIN烧录孔</x:v>
       </x:c>
       <x:c r="R10" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C5138889.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C492420.html</x:v>
       </x:c>
       <x:c r="S10" s="7" t="str">
-        <x:v>Package: Through Hole,P=1mm; Connector Type: Through Hole; Pitch: 1mm; Circluar Pins/Square Pins: Square pin; Current Rating: 1A; Insulation Height: 1mm; Length of Mating Pin: 3.55mm; Contact Plating: Gold; Length of End Connection Pin: 1.8mm; Contact Material: Phosphor bronze; Number of PINs: 5P; Operating Temperature: -40℃~+105℃; Pin Structure: 1x5P; Number of Rows: 1</x:v>
+        <x:v>Package: Through Hole,P=2.54mm; Connector Type: Through Hole; Voltage Rating (Max): -; Contact Material: Brass; Number of Rows: 2; Pitch: 2.54mm; Circluar Pins/Square Pins: Square pin; Current Rating: 3A; Insulation Height: 2.5mm; Length of Mating Pin: 6mm; Number of PINs: 6P; Operating Temperature: -40℃~+105℃; Length of End Connection Pin: 3mm; Contact Plating: Gold; Color: Black; Pin Structure: 2x3P; Row Spacing: 2.54mm</x:v>
       </x:c>
       <x:c r="T10" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: J11</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: J8</x:v>
       </x:c>
       <x:c r="U10" s="7" t="str">
         <x:v>METADATA_READY</x:v>
@@ -8889,39 +9447,39 @@
     </x:row>
     <x:row r="11" ht="24" customHeight="1">
       <x:c r="A11" s="7" t="str">
-        <x:v>C54334395</x:v>
+        <x:v>C5138889</x:v>
       </x:c>
       <x:c r="B11" s="7" t="str">
-        <x:v>GT-A0801WRS-108BBT01</x:v>
+        <x:v>GPCA101-0502A001C1AA</x:v>
       </x:c>
       <x:c r="C11" s="7" t="str">
-        <x:v>G-Switch</x:v>
+        <x:v>GREENCONN</x:v>
       </x:c>
       <x:c r="D11" s="7" t="str">
-        <x:v>Surface Mount, Right Angle 100V 8 1 0.8mm 800mA 8P -40℃~+85℃ Tin Black 1x8P SMD,P=0.8mm,Surface Mount,Right Angle Headers, Male Pins</x:v>
+        <x:v>Pin Header 5 Position 1mm Pitch Single Row Through Hole -40℃~+105℃</x:v>
       </x:c>
       <x:c r="E11" s="7" t="str">
         <x:v>Connectors/Headers, Male Pins</x:v>
       </x:c>
       <x:c r="F11" s="7" t="str">
-        <x:v>GT-A0801WRS-108BBT01</x:v>
+        <x:v>GPCA101-0502A001C1AA</x:v>
       </x:c>
       <x:c r="G11" s="7" t="str">
         <x:v>ExternalDriver_</x:v>
       </x:c>
       <x:c r="H11" s="7" t="str">
-        <x:v>9990000051497</x:v>
+        <x:v>GPCA101-0502A</x:v>
       </x:c>
       <x:c r="I11" s="7" t="str">
-        <x:v>SMD,P=0.8mm,Surface Mount,Right Angle</x:v>
+        <x:v>Through Hole,P=1mm</x:v>
       </x:c>
       <x:c r="J11" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/280a0ac82606d05a19e9b62f8ac57389.pdf?productCode=C54334395</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/9791ba8c859df0647813150b8f9162a2.pdf?productCode=C5138889</x:v>
       </x:c>
       <x:c r="K11" s="7" t="str"/>
       <x:c r="L11" s="7" t="str"/>
       <x:c r="M11" s="7" t="str">
-        <x:v>../datasheets/C54334395/GT-A0801WRS-108BBT01.pdf</x:v>
+        <x:v>../datasheets/C5138889/GPCA101-0502A001C1AA.pdf</x:v>
       </x:c>
       <x:c r="N11" s="7" t="str"/>
       <x:c r="O11" s="7" t="str">
@@ -8931,16 +9489,16 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q11" s="7" t="str">
-        <x:v>接插件</x:v>
+        <x:v>插件</x:v>
       </x:c>
       <x:c r="R11" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C54334395.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C5138889.html</x:v>
       </x:c>
       <x:c r="S11" s="7" t="str">
-        <x:v>Package: SMD,P=0.8mm,Surface Mount,Right Angle; Connector Type: Surface Mount, Right Angle; Voltage Rating (Max): 100V; Contact Material: Brass; Number of PINs Per Row: 8; Number of Rows: 1; Pitch: 0.8mm; Current Rating: 800mA; Flame Retardant Rating: UL94V-0; Number of PINs: 8P; Operating Temperature: -40℃~+85℃; Contact Plating: Tin; Plastic Material: LCP; Color: Black; Pin Structure: 1x8P</x:v>
+        <x:v>Package: Through Hole,P=1mm; Connector Type: Through Hole; Pitch: 1mm; Circluar Pins/Square Pins: Square pin; Current Rating: 1A; Insulation Height: 1mm; Length of Mating Pin: 3.55mm; Contact Plating: Gold; Length of End Connection Pin: 1.8mm; Contact Material: Phosphor bronze; Number of PINs: 5P; Operating Temperature: -40℃~+105℃; Pin Structure: 1x5P; Number of Rows: 1</x:v>
       </x:c>
       <x:c r="T11" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: J9</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: J11</x:v>
       </x:c>
       <x:c r="U11" s="7" t="str">
         <x:v>METADATA_READY</x:v>
@@ -8949,13 +9507,75 @@
         <x:v>legacy_import</x:v>
       </x:c>
     </x:row>
+    <x:row r="12" ht="24" customHeight="1">
+      <x:c r="A12" s="7" t="str">
+        <x:v>C54334395</x:v>
+      </x:c>
+      <x:c r="B12" s="7" t="str">
+        <x:v>GT-A0801WRS-108BBT01</x:v>
+      </x:c>
+      <x:c r="C12" s="7" t="str">
+        <x:v>G-Switch</x:v>
+      </x:c>
+      <x:c r="D12" s="7" t="str">
+        <x:v>Surface Mount, Right Angle 100V 8 1 0.8mm 800mA 8P -40℃~+85℃ Tin Black 1x8P SMD,P=0.8mm,Surface Mount,Right Angle Headers, Male Pins</x:v>
+      </x:c>
+      <x:c r="E12" s="7" t="str">
+        <x:v>Connectors/Headers, Male Pins</x:v>
+      </x:c>
+      <x:c r="F12" s="7" t="str">
+        <x:v>GT-A0801WRS-108BBT01</x:v>
+      </x:c>
+      <x:c r="G12" s="7" t="str">
+        <x:v>ExternalDriver_</x:v>
+      </x:c>
+      <x:c r="H12" s="7" t="str">
+        <x:v>9990000051497</x:v>
+      </x:c>
+      <x:c r="I12" s="7" t="str">
+        <x:v>SMD,P=0.8mm,Surface Mount,Right Angle</x:v>
+      </x:c>
+      <x:c r="J12" s="7" t="str">
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/280a0ac82606d05a19e9b62f8ac57389.pdf?productCode=C54334395</x:v>
+      </x:c>
+      <x:c r="K12" s="7" t="str"/>
+      <x:c r="L12" s="7" t="str"/>
+      <x:c r="M12" s="7" t="str">
+        <x:v>../datasheets/C54334395/GT-A0801WRS-108BBT01.pdf</x:v>
+      </x:c>
+      <x:c r="N12" s="7" t="str"/>
+      <x:c r="O12" s="7" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="P12" s="7" t="str">
+        <x:v>LCSC</x:v>
+      </x:c>
+      <x:c r="Q12" s="7" t="str">
+        <x:v>接插件</x:v>
+      </x:c>
+      <x:c r="R12" s="7" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C54334395.html</x:v>
+      </x:c>
+      <x:c r="S12" s="7" t="str">
+        <x:v>Package: SMD,P=0.8mm,Surface Mount,Right Angle; Connector Type: Surface Mount, Right Angle; Voltage Rating (Max): 100V; Contact Material: Brass; Number of PINs Per Row: 8; Number of Rows: 1; Pitch: 0.8mm; Current Rating: 800mA; Flame Retardant Rating: UL94V-0; Number of PINs: 8P; Operating Temperature: -40℃~+85℃; Contact Plating: Tin; Plastic Material: LCP; Color: Black; Pin Structure: 1x8P</x:v>
+      </x:c>
+      <x:c r="T12" s="7" t="str">
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: J9</x:v>
+      </x:c>
+      <x:c r="U12" s="7" t="str">
+        <x:v>METADATA_READY</x:v>
+      </x:c>
+      <x:c r="V12" s="7" t="str">
+        <x:v>legacy_import</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="U5:U11">
+  <x:conditionalFormatting sqref="U5:U12">
     <x:cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="CLASSIFIED_PARTIAL"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65ff460627604f98"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbaed6026420441cf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9134,7 +9754,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99d7a46294c0477c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R448e6aba9872454c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9375,7 +9995,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf5ab5ef593364656"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06d7c907b8724fce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9612,7 +10232,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R94000f9200774fa3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f9b7ddb9d4b4166"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9853,7 +10473,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5bc53881a9fd4795"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R265d35ed9ed840d7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10094,7 +10714,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61944fca74a34022"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d7efffb3502487f"/>
   </x:tableParts>
 </x:worksheet>
 </file>